--- a/assets/data/Yi_Capital_US.xlsx
+++ b/assets/data/Yi_Capital_US.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="4" t="n">
-        <v>1388</v>
+        <v>2809.86</v>
       </c>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
@@ -2234,6 +2234,39 @@
         <v>138.8</v>
       </c>
       <c r="I57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Oracle Corporation</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>1421.86</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="I58" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2260,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4706,12 +4739,12 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>ETF Stock Buy Record</t>
+          <t>ETF Stock Dividend Record</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
@@ -4721,10 +4754,10 @@
         <v>-16538.54</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>-1388</v>
+        <v>61.23</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>-17926.54</v>
+        <v>-16477.31</v>
       </c>
     </row>
     <row r="103">
@@ -4735,20 +4768,188 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>ETF Stock Sell Record</t>
+          <t>ETF Stock Buy Record</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>-17926.54</v>
+        <v>-16477.31</v>
       </c>
       <c r="E103" s="9" t="n">
+        <v>-1388</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>-17865.31</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>-17865.31</v>
+      </c>
+      <c r="E104" s="9" t="n">
         <v>406.8</v>
       </c>
-      <c r="F103" s="9" t="n">
-        <v>-17519.74</v>
+      <c r="F104" s="9" t="n">
+        <v>-17458.51</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>-17458.51</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>-17094.55</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>-17094.55</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>-17050.02</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>-17050.02</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>-17018.97</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>-17018.97</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>-17017.22</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Buy Record</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>-17017.22</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>-1421.86</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>-18439.08</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>-18439.08</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>5630</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>-12809.08</v>
       </c>
     </row>
   </sheetData>
@@ -4762,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5074,7 +5275,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>153121.43</v>
+        <v>153121.44</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0</v>
@@ -5083,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>153121.43</v>
+        <v>153121.44</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>1513476.32</v>
@@ -5098,7 +5299,7 @@
         <v>13619.69</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>139501.74</v>
+        <v>139501.75</v>
       </c>
     </row>
     <row r="10">
@@ -5108,7 +5309,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>153368.67</v>
+        <v>153368.68</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>0</v>
@@ -5117,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>153368.67</v>
+        <v>153368.68</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>1513476.32</v>
@@ -5132,7 +5333,7 @@
         <v>13619.69</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>139748.98</v>
+        <v>139748.99</v>
       </c>
     </row>
     <row r="11">
@@ -5414,7 +5615,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>155929.19</v>
+        <v>155929.2</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -5423,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>155929.19</v>
+        <v>155929.2</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>1513476.32</v>
@@ -5438,7 +5639,7 @@
         <v>27249.8</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>128679.39</v>
+        <v>128679.4</v>
       </c>
     </row>
     <row r="20">
@@ -5448,7 +5649,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>205195.01</v>
+        <v>205195.02</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
@@ -5457,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>205195.01</v>
+        <v>205195.02</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>2005476.32</v>
@@ -5472,7 +5673,7 @@
         <v>39507.2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>165687.81</v>
+        <v>165687.82</v>
       </c>
     </row>
     <row r="21">
@@ -5550,7 +5751,7 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>208407.89</v>
+        <v>208407.9</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0</v>
@@ -5559,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>208407.89</v>
+        <v>208407.9</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>2054841.55</v>
@@ -5574,7 +5775,7 @@
         <v>13000.1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>195407.79</v>
+        <v>195407.8</v>
       </c>
     </row>
     <row r="24">
@@ -5584,7 +5785,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>206929.19</v>
+        <v>206929.2</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
@@ -5593,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>206929.19</v>
+        <v>206929.2</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>2054841.55</v>
@@ -5608,7 +5809,7 @@
         <v>13000.1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>193929.09</v>
+        <v>193929.1</v>
       </c>
     </row>
     <row r="25">
@@ -5686,7 +5887,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
@@ -5695,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>2107072.57</v>
@@ -5710,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
     </row>
     <row r="28">
@@ -5720,7 +5921,7 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>214482.65</v>
+        <v>214482.66</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>0</v>
@@ -5729,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>214482.65</v>
+        <v>214482.66</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>2107072.57</v>
@@ -5744,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>214482.65</v>
+        <v>214482.66</v>
       </c>
     </row>
     <row r="29">
@@ -5822,7 +6023,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>212741.95</v>
+        <v>212741.94</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>0</v>
@@ -5831,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>212741.95</v>
+        <v>212741.94</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>2107072.57</v>
@@ -5846,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>212741.95</v>
+        <v>212741.94</v>
       </c>
     </row>
     <row r="32">
@@ -6876,7 +7077,7 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>212156.27</v>
+        <v>212156.26</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>0</v>
@@ -6885,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>212156.27</v>
+        <v>212156.26</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>2107072.57</v>
@@ -6900,7 +7101,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>217888.28</v>
+        <v>217888.27</v>
       </c>
     </row>
     <row r="63">
@@ -7046,7 +7247,7 @@
         </is>
       </c>
       <c r="B67" s="9" t="n">
-        <v>213605</v>
+        <v>213604.99</v>
       </c>
       <c r="C67" s="9" t="n">
         <v>0</v>
@@ -7055,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>213605</v>
+        <v>213604.99</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>2107072.57</v>
@@ -7070,7 +7271,7 @@
         <v>-5521.95</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>219126.95</v>
+        <v>219126.94</v>
       </c>
     </row>
     <row r="68">
@@ -9052,7 +9253,7 @@
         </is>
       </c>
       <c r="B126" s="9" t="n">
-        <v>221887.09</v>
+        <v>221948.32</v>
       </c>
       <c r="C126" s="9" t="n">
         <v>0</v>
@@ -9061,19 +9262,19 @@
         <v>0</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>221887.09</v>
+        <v>221948.32</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G126" s="16" t="n">
-        <v>0.105306</v>
+        <v>0.105335</v>
       </c>
       <c r="H126" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>-16538.54</v>
+        <v>-16477.31</v>
       </c>
       <c r="J126" s="9" t="n">
         <v>238425.63</v>
@@ -9086,7 +9287,7 @@
         </is>
       </c>
       <c r="B127" s="9" t="n">
-        <v>223453.64</v>
+        <v>223514.87</v>
       </c>
       <c r="C127" s="9" t="n">
         <v>0</v>
@@ -9095,19 +9296,19 @@
         <v>0</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>223453.64</v>
+        <v>223514.87</v>
       </c>
       <c r="F127" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G127" s="16" t="n">
-        <v>0.106049</v>
+        <v>0.106078</v>
       </c>
       <c r="H127" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17458.51</v>
       </c>
       <c r="J127" s="9" t="n">
         <v>240973.38</v>
@@ -9120,7 +9321,7 @@
         </is>
       </c>
       <c r="B128" s="9" t="n">
-        <v>221746.61</v>
+        <v>221829.33</v>
       </c>
       <c r="C128" s="9" t="n">
         <v>0</v>
@@ -9129,22 +9330,22 @@
         <v>0</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>221746.61</v>
+        <v>221829.33</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G128" s="16" t="n">
-        <v>0.105239</v>
+        <v>0.105278</v>
       </c>
       <c r="H128" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17050.02</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>239266.35</v>
+        <v>238879.35</v>
       </c>
     </row>
     <row r="129">
@@ -9154,7 +9355,7 @@
         </is>
       </c>
       <c r="B129" s="9" t="n">
-        <v>222272.13</v>
+        <v>222341.17</v>
       </c>
       <c r="C129" s="9" t="n">
         <v>0</v>
@@ -9163,22 +9364,22 @@
         <v>0</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>222272.13</v>
+        <v>222341.17</v>
       </c>
       <c r="F129" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G129" s="16" t="n">
-        <v>0.105489</v>
+        <v>0.105521</v>
       </c>
       <c r="H129" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17050.02</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>239791.87</v>
+        <v>239391.19</v>
       </c>
     </row>
     <row r="130">
@@ -9188,7 +9389,7 @@
         </is>
       </c>
       <c r="B130" s="9" t="n">
-        <v>223492</v>
+        <v>223618.37</v>
       </c>
       <c r="C130" s="9" t="n">
         <v>0</v>
@@ -9197,22 +9398,22 @@
         <v>0</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>223492</v>
+        <v>223618.37</v>
       </c>
       <c r="F130" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G130" s="16" t="n">
-        <v>0.106068</v>
+        <v>0.106128</v>
       </c>
       <c r="H130" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17018.97</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>241011.74</v>
+        <v>240637.34</v>
       </c>
     </row>
     <row r="131">
@@ -9222,7 +9423,7 @@
         </is>
       </c>
       <c r="B131" s="9" t="n">
-        <v>225633.76</v>
+        <v>225771.6</v>
       </c>
       <c r="C131" s="9" t="n">
         <v>0</v>
@@ -9231,22 +9432,22 @@
         <v>0</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>225633.76</v>
+        <v>225771.6</v>
       </c>
       <c r="F131" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G131" s="16" t="n">
-        <v>0.107084</v>
+        <v>0.107149</v>
       </c>
       <c r="H131" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17017.22</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>243153.5</v>
+        <v>242788.82</v>
       </c>
     </row>
     <row r="132">
@@ -9256,7 +9457,7 @@
         </is>
       </c>
       <c r="B132" s="9" t="n">
-        <v>225633.76</v>
+        <v>223868.53</v>
       </c>
       <c r="C132" s="9" t="n">
         <v>0</v>
@@ -9265,22 +9466,56 @@
         <v>0</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>225633.76</v>
+        <v>223868.53</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G132" s="16" t="n">
-        <v>0.107084</v>
+        <v>0.106246</v>
       </c>
       <c r="H132" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-18439.08</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>243153.5</v>
+        <v>242307.61</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="n">
+        <v>228717</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>228717</v>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G133" s="16" t="n">
+        <v>0.108547</v>
+      </c>
+      <c r="H133" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I133" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>241526.08</v>
       </c>
     </row>
   </sheetData>
@@ -9294,7 +9529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10424,7 +10659,7 @@
       </c>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="4" t="n">
-        <v>406.8</v>
+        <v>6400.76</v>
       </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
@@ -10509,6 +10744,72 @@
         <v>20.34</v>
       </c>
       <c r="I42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>MBGL</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Mobility Global Inc.</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>PayPal Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>5630</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10537,7 +10838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11882,11 +12183,195 @@
       </c>
       <c r="H49" s="7" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2026/07/01-2026/07/31</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Total Dividend Amount:</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="4" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Trade No.</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Stock/ETF Name</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Div Per Share (USD)</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>PBR-A</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras (Preferred ADR)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>0.10205</v>
+      </c>
+      <c r="H53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>iShares 20+ Year Treasury Bond ETF</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="H54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>SGOV</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>iShares 0-3 Month Treasury Bond ETF</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="H55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>PGR</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>The Progressive Corporation</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H56" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="D32:E32"/>
@@ -12057,7 +12542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12085,7 +12570,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -12103,7 +12588,7 @@
       </c>
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="4" t="n">
-        <v>240276.88</v>
+        <v>241526.45</v>
       </c>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
@@ -12203,13 +12688,13 @@
         <v>20</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>428.1900024414062</v>
+        <v>423.1400146484375</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>8563.800048828125</v>
+        <v>8462.80029296875</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>0.03564138202803051</v>
+        <v>0.03503881394080345</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>6893.1</v>
@@ -12224,13 +12709,13 @@
         <v>6893.1</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>1734.120048828125</v>
+        <v>1633.12029296875</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>0.2423728146738223</v>
+        <v>0.2277205165990265</v>
       </c>
       <c r="N3" s="15" t="n">
-        <v>0.2515733195265011</v>
+        <v>0.2369210214517053</v>
       </c>
       <c r="O3" s="7" t="n"/>
     </row>
@@ -12252,13 +12737,13 @@
         <v>150</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>74.33000183105469</v>
+        <v>73.59020233154297</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>11149.5002746582</v>
+        <v>11038.53034973145</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.04640271800426989</v>
+        <v>0.04570319488993528</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>12219</v>
@@ -12273,13 +12758,13 @@
         <v>12219</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>-1069.499725341795</v>
+        <v>-1180.469650268553</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>-0.0875275984402812</v>
+        <v>-0.09660935021430181</v>
       </c>
       <c r="N4" s="15" t="n">
-        <v>-0.08752759844028114</v>
+        <v>-0.09660935021430175</v>
       </c>
       <c r="O4" s="7" t="n"/>
     </row>
@@ -12301,13 +12786,13 @@
         <v>20</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>377.489990234375</v>
+        <v>371.4349975585938</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>7549.7998046875</v>
+        <v>7428.699951171875</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0.03142124962514032</v>
+        <v>0.03075729385076347</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>22085.17</v>
@@ -12322,13 +12807,13 @@
         <v>9410.169999999998</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>-1860.370195312498</v>
+        <v>-1981.470048828123</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>-0.1976978306781385</v>
+        <v>-0.2105668706121275</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>-0.08423617274906638</v>
+        <v>-0.08971948365478388</v>
       </c>
       <c r="O5" s="7" t="n"/>
     </row>
@@ -12350,13 +12835,13 @@
         <v>600</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>14.98999977111816</v>
+        <v>15.85999965667725</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>8993.999862670898</v>
+        <v>9515.999794006348</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.03743181569370865</v>
+        <v>0.03939941091602262</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>11165</v>
@@ -12365,19 +12850,19 @@
         <v>6936</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>229.77</v>
+        <v>291</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>4229</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>4994.769862670899</v>
+        <v>5577.999794006348</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>1.126743878616907</v>
+        <v>1.25017729818074</v>
       </c>
       <c r="N6" s="15" t="n">
-        <v>0.4473595936113658</v>
+        <v>0.4995969363194221</v>
       </c>
       <c r="O6" s="7" t="n"/>
     </row>
@@ -12399,13 +12884,13 @@
         <v>107</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>221.5399932861328</v>
+        <v>225.6849975585938</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>23704.77928161621</v>
+        <v>24148.29473876953</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0.09865609769600341</v>
+        <v>0.0999819890636468</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>28073.97</v>
@@ -12420,13 +12905,13 @@
         <v>28073.97</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>-4369.19071838379</v>
+        <v>-3925.67526123047</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>-0.1556313808978136</v>
+        <v>-0.1398332783439774</v>
       </c>
       <c r="N7" s="15" t="n">
-        <v>-0.1556313808978135</v>
+        <v>-0.1398332783439774</v>
       </c>
       <c r="O7" s="7" t="n"/>
     </row>
@@ -12448,13 +12933,13 @@
         <v>43</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>388.8399963378906</v>
+        <v>396.0132141113281</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>16720.1198425293</v>
+        <v>17028.56820678711</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.06958688613281989</v>
+        <v>0.07050394815196401</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>17698.7</v>
@@ -12469,13 +12954,13 @@
         <v>17698.7</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>-915.9701574707033</v>
+        <v>-607.5217932128908</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>-0.05529107547281454</v>
+        <v>-0.03786333421171556</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>-0.05175352751731501</v>
+        <v>-0.03432578625621604</v>
       </c>
       <c r="O8" s="7" t="n"/>
     </row>
@@ -12497,13 +12982,13 @@
         <v>500</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>27.05999946594238</v>
+        <v>28.22999954223633</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>13529.99973297119</v>
+        <v>14114.99977111816</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0.0563100360321894</v>
+        <v>0.05844080370957171</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>12425</v>
@@ -12518,13 +13003,13 @@
         <v>12425</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1104.999732971191</v>
+        <v>1689.999771118164</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>0.08893358011840569</v>
+        <v>0.1360160781584035</v>
       </c>
       <c r="N9" s="15" t="n">
-        <v>0.08893358011840574</v>
+        <v>0.1360160781584036</v>
       </c>
       <c r="O9" s="7" t="n"/>
     </row>
@@ -12546,13 +13031,13 @@
         <v>25</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>234.3999938964844</v>
+        <v>209.9700012207031</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5859.999847412109</v>
+        <v>5249.250030517578</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0.02438852986465931</v>
+        <v>0.02173364474887549</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>5210</v>
@@ -12561,19 +13046,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>5210</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>651.7498474121094</v>
+        <v>42.75003051757812</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>0.1247600474879288</v>
+        <v>0.007533595108940112</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>0.1250959400023243</v>
+        <v>0.008205380137730926</v>
       </c>
       <c r="O10" s="7" t="n"/>
     </row>
@@ -12595,13 +13080,13 @@
         <v>430</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>37.09999847412109</v>
+        <v>37.125</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>15952.99934387207</v>
+        <v>15963.75</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0.06639423396926115</v>
+        <v>0.06609524586232211</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>17180.9</v>
@@ -12616,13 +13101,13 @@
         <v>17180.9</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>-1087.390656127931</v>
+        <v>-1076.640000000001</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.0714689367918987</v>
+        <v>-0.07084320379025562</v>
       </c>
       <c r="N11" s="15" t="n">
-        <v>-0.06329066906436397</v>
+        <v>-0.06266493606272087</v>
       </c>
       <c r="O11" s="7" t="n"/>
     </row>
@@ -12644,13 +13129,13 @@
         <v>200</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>23.40999984741211</v>
+        <v>23.61499977111816</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4681.999969482422</v>
+        <v>4722.999954223633</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>0.01948585308111966</v>
+        <v>0.01955479402910639</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>5947</v>
@@ -12665,13 +13150,13 @@
         <v>5947</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>-1218.800030517578</v>
+        <v>-1177.800045776367</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.2127122970434804</v>
+        <v>-0.2058180672231995</v>
       </c>
       <c r="N12" s="15" t="n">
-        <v>-0.2049436742084376</v>
+        <v>-0.1980494443881566</v>
       </c>
       <c r="O12" s="7" t="n"/>
     </row>
@@ -12693,13 +13178,13 @@
         <v>120</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>128.2200012207031</v>
+        <v>125.8949966430664</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>15386.40014648438</v>
+        <v>15107.39959716797</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0.06403612444595044</v>
+        <v>0.06254966976525959</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>14520</v>
@@ -12714,13 +13199,13 @@
         <v>14520</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1070.880146484375</v>
+        <v>791.8795971679683</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>0.05966943157605888</v>
+        <v>0.04045451771129261</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.07375207620415802</v>
+        <v>0.05453716233939176</v>
       </c>
       <c r="O13" s="7" t="n"/>
     </row>
@@ -12739,19 +13224,19 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>141.6000061035156</v>
+        <v>131.5500030517578</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>5522.400238037109</v>
+        <v>7893.000183105469</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0.02298348577422718</v>
+        <v>0.03267965156643705</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>17927.57</v>
+        <v>20737.43</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>15703.6</v>
@@ -12760,16 +13245,16 @@
         <v>28</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2223.969999999999</v>
+        <v>5033.83</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3326.430238037108</v>
+        <v>2887.170183105467</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>1.483127127630818</v>
+        <v>0.5679910094511473</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.1855483056564335</v>
+        <v>0.1392250719161182</v>
       </c>
       <c r="O14" s="7" t="n"/>
     </row>
@@ -12791,13 +13276,13 @@
         <v>40</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>352.2000122070312</v>
+        <v>357.4100036621094</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>14088.00048828125</v>
+        <v>14296.40014648438</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0.0586323599980154</v>
+        <v>0.05919186172597432</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>12988</v>
@@ -12812,13 +13297,13 @@
         <v>12988</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1118.76048828125</v>
+        <v>1327.160146484375</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>0.0846936008839891</v>
+        <v>0.100739155103509</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.086138011108812</v>
+        <v>0.1021835653283319</v>
       </c>
       <c r="O15" s="7" t="n"/>
     </row>
@@ -12840,13 +13325,13 @@
         <v>200</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>84.55000305175781</v>
+        <v>84.36499786376953</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>16910.00061035156</v>
+        <v>16872.99957275391</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0.07037714430642766</v>
+        <v>0.06985984215463317</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>17734</v>
@@ -12855,19 +13340,19 @@
         <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>136.57</v>
+        <v>181.1</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>17734</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>-687.4293896484378</v>
+        <v>-679.9004272460952</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.04646438421385124</v>
+        <v>-0.04855083045258227</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.03876335793664361</v>
+        <v>-0.03833880834815018</v>
       </c>
       <c r="O16" s="7" t="n"/>
     </row>
@@ -12889,13 +13374,13 @@
         <v>150</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>100.4599990844727</v>
+        <v>100.5363006591797</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>15068.9998626709</v>
+        <v>15080.44509887695</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0.06271514722711061</v>
+        <v>0.06243806915815661</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>16683</v>
@@ -12904,19 +13389,19 @@
         <v>1607.52</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>93.29000000000001</v>
+        <v>124.34</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>15075.48</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>86.80986267089975</v>
+        <v>129.3050988769537</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>-0.0004298461693491978</v>
+        <v>0.0003293493060887112</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>0.005203492337762977</v>
+        <v>0.007750710236585369</v>
       </c>
       <c r="O17" s="7" t="n"/>
     </row>
@@ -12938,13 +13423,13 @@
         <v>150</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>49.63999938964844</v>
+        <v>50.9098014831543</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>7445.999908447266</v>
+        <v>7636.470222473145</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0.03098924844163833</v>
+        <v>0.03161753202566215</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>5769</v>
@@ -12959,13 +13444,13 @@
         <v>5769</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1808.059908447266</v>
+        <v>1998.530222473145</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.2906916117953312</v>
+        <v>0.3237077868734866</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.3134095871810134</v>
+        <v>0.3464257622591688</v>
       </c>
       <c r="O18" s="7" t="n"/>
     </row>
@@ -12984,37 +13469,37 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>45.65000152587891</v>
+        <v>54.7400016784668</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>18260.00061035156</v>
+        <v>16422.00050354004</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0.07599566242496143</v>
+        <v>0.06799255568601716</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>18236.4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>39.2</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>18236.4</v>
+        <v>12606.4</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>62.80061035156177</v>
+        <v>3854.800503540038</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>0.001294148535432545</v>
+        <v>0.3026716987831607</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.003443695595159229</v>
+        <v>0.2113794665361605</v>
       </c>
       <c r="O19" s="7" t="n"/>
     </row>
@@ -13036,13 +13521,13 @@
         <v>40</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>196.9299926757812</v>
+        <v>209.4550018310547</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>7877.19970703125</v>
+        <v>8378.200073242188</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0.03278384390908443</v>
+        <v>0.03468854083311675</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>8635</v>
@@ -13057,13 +13542,13 @@
         <v>8635</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-757.80029296875</v>
+        <v>-256.7999267578125</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>-0.08775915378908512</v>
+        <v>-0.02973942405996671</v>
       </c>
       <c r="N20" s="15" t="n">
-        <v>-0.08775915378908512</v>
+        <v>-0.02973942405996671</v>
       </c>
       <c r="O20" s="7" t="n"/>
     </row>
@@ -13085,13 +13570,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>535.3800048828125</v>
+        <v>515.9500122070312</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>5353.800048828125</v>
+        <v>5159.500122070312</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>0.02228179450173911</v>
+        <v>0.02136205021344723</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>5069.8</v>
@@ -13106,13 +13591,13 @@
         <v>5069.8</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>284.0000488281248</v>
+        <v>89.70012207031232</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>0.05601799850647458</v>
+        <v>0.01769302971918267</v>
       </c>
       <c r="N21" s="15" t="n">
-        <v>0.05601799850647458</v>
+        <v>0.01769302971918267</v>
       </c>
       <c r="O21" s="7" t="n"/>
     </row>
@@ -13134,16 +13619,16 @@
         <v>38</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>443.4599914550781</v>
+        <v>447.5299987792969</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>16851.47967529297</v>
+        <v>17006.13995361328</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>0.07013358805906453</v>
+        <v>0.07041108770828464</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>14284.37917736824</v>
+        <v>14284.70668805384</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
@@ -13152,67 +13637,18 @@
         <v>51.6</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>14284.37917736824</v>
+        <v>14284.70668805384</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>2618.700497924729</v>
+        <v>2773.033265559436</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>0.1797138304751787</v>
+        <v>0.190513765874895</v>
       </c>
       <c r="N22" s="15" t="n">
-        <v>0.1833261680755242</v>
+        <v>0.1941260206538574</v>
       </c>
       <c r="O22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>MBGL</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Mobility Global Inc.</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>21.20000076293945</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>805.6000289916992</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>0.003352798784578661</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>729.7608226317609</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>729.7608226317609</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>75.83920635993832</v>
-      </c>
-      <c r="M23" s="15" t="n">
-        <v>0.1039233732587026</v>
-      </c>
-      <c r="N23" s="15" t="n">
-        <v>0.1039233732587025</v>
-      </c>
-      <c r="O23" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/data/Yi_Capital_US.xlsx
+++ b/assets/data/Yi_Capital_US.xlsx
@@ -4963,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>153121.44</v>
+        <v>153121.43</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>153121.44</v>
+        <v>153121.43</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>1513476.32</v>
@@ -5299,7 +5299,7 @@
         <v>13619.69</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>139501.75</v>
+        <v>139501.74</v>
       </c>
     </row>
     <row r="10">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>153368.68</v>
+        <v>153368.67</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>0</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>153368.68</v>
+        <v>153368.67</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>1513476.32</v>
@@ -5333,7 +5333,7 @@
         <v>13619.69</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>139748.99</v>
+        <v>139748.98</v>
       </c>
     </row>
     <row r="11">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>155929.2</v>
+        <v>155929.19</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>155929.2</v>
+        <v>155929.19</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>1513476.32</v>
@@ -5639,7 +5639,7 @@
         <v>27249.8</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>128679.4</v>
+        <v>128679.39</v>
       </c>
     </row>
     <row r="20">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>205195.02</v>
+        <v>205195.01</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>205195.02</v>
+        <v>205195.01</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>2005476.32</v>
@@ -5673,7 +5673,7 @@
         <v>39507.2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>165687.82</v>
+        <v>165687.81</v>
       </c>
     </row>
     <row r="21">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>204602.42</v>
+        <v>204602.43</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>204602.42</v>
+        <v>204602.43</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>2005476.32</v>
@@ -5707,7 +5707,7 @@
         <v>39507.2</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>165095.22</v>
+        <v>165095.23</v>
       </c>
     </row>
     <row r="22">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>208407.9</v>
+        <v>208407.89</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0</v>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>208407.9</v>
+        <v>208407.89</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>2054841.55</v>
@@ -5775,7 +5775,7 @@
         <v>13000.1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>195407.8</v>
+        <v>195407.79</v>
       </c>
     </row>
     <row r="24">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>206929.2</v>
+        <v>206929.19</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
@@ -5794,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>206929.2</v>
+        <v>206929.19</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>2054841.55</v>
@@ -5809,7 +5809,7 @@
         <v>13000.1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>193929.1</v>
+        <v>193929.09</v>
       </c>
     </row>
     <row r="25">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>214482.66</v>
+        <v>214482.65</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>214482.66</v>
+        <v>214482.65</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>2107072.57</v>
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>214482.66</v>
+        <v>214482.65</v>
       </c>
     </row>
     <row r="29">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>2107072.57</v>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
     </row>
     <row r="34">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>217434.09</v>
+        <v>217434.08</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>0</v>
@@ -6304,13 +6304,13 @@
         <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>217434.09</v>
+        <v>217434.08</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>0.103193</v>
+        <v>0.103192</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>-0</v>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>217434.09</v>
+        <v>217434.08</v>
       </c>
     </row>
     <row r="40">
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>215143.4</v>
+        <v>215143.41</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>215143.4</v>
+        <v>215143.41</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>2107072.57</v>
@@ -6761,7 +6761,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>227885.84</v>
+        <v>227885.85</v>
       </c>
     </row>
     <row r="53">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="B55" s="9" t="n">
-        <v>213029.51</v>
+        <v>213029.52</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>0</v>
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>213029.51</v>
+        <v>213029.52</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>2107072.57</v>
@@ -6863,7 +6863,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>225771.95</v>
+        <v>225771.96</v>
       </c>
     </row>
     <row r="56">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>210102.87</v>
+        <v>210102.88</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>210102.87</v>
+        <v>210102.88</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>2107072.57</v>
@@ -6897,7 +6897,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>222845.31</v>
+        <v>222845.32</v>
       </c>
     </row>
     <row r="57">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>210662.18</v>
+        <v>210662.17</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>210662.18</v>
+        <v>210662.17</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>2107072.57</v>
@@ -7033,7 +7033,7 @@
         <v>-5792.88</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>216455.06</v>
+        <v>216455.05</v>
       </c>
     </row>
     <row r="61">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B67" s="9" t="n">
-        <v>213604.99</v>
+        <v>213605</v>
       </c>
       <c r="C67" s="9" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>213604.99</v>
+        <v>213605</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>2107072.57</v>
@@ -7271,7 +7271,7 @@
         <v>-5521.95</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>219126.94</v>
+        <v>219126.95</v>
       </c>
     </row>
     <row r="68">
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>211847.57</v>
+        <v>211847.56</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>211847.57</v>
+        <v>211847.56</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>2107072.57</v>
@@ -7305,7 +7305,7 @@
         <v>-5521.95</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>217369.52</v>
+        <v>217369.51</v>
       </c>
     </row>
     <row r="69">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B81" s="9" t="n">
-        <v>223631.68</v>
+        <v>223631.67</v>
       </c>
       <c r="C81" s="9" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>223631.68</v>
+        <v>223631.67</v>
       </c>
       <c r="F81" s="8" t="n">
         <v>2107072.57</v>
@@ -7747,7 +7747,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>227303.18</v>
+        <v>227303.17</v>
       </c>
     </row>
     <row r="82">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="B97" s="9" t="n">
-        <v>220861.6</v>
+        <v>220861.61</v>
       </c>
       <c r="C97" s="9" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>220861.6</v>
+        <v>220861.61</v>
       </c>
       <c r="F97" s="8" t="n">
         <v>2107072.57</v>
@@ -8291,7 +8291,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>225765.16</v>
+        <v>225765.17</v>
       </c>
     </row>
     <row r="98">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="B101" s="9" t="n">
-        <v>220806.2</v>
+        <v>220806.21</v>
       </c>
       <c r="C101" s="9" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>220806.2</v>
+        <v>220806.21</v>
       </c>
       <c r="F101" s="8" t="n">
         <v>2107072.57</v>
@@ -8427,7 +8427,7 @@
         <v>-2876.06</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>223682.26</v>
+        <v>223682.27</v>
       </c>
     </row>
     <row r="102">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="B133" s="9" t="n">
-        <v>228717</v>
+        <v>228347.57</v>
       </c>
       <c r="C133" s="9" t="n">
         <v>0</v>
@@ -9500,13 +9500,13 @@
         <v>0</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>228717</v>
+        <v>228347.57</v>
       </c>
       <c r="F133" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G133" s="16" t="n">
-        <v>0.108547</v>
+        <v>0.108372</v>
       </c>
       <c r="H133" s="9" t="n">
         <v>-0</v>
@@ -9515,7 +9515,75 @@
         <v>-12809.08</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>241526.08</v>
+        <v>241156.65</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G134" s="16" t="n">
+        <v>0.109755</v>
+      </c>
+      <c r="H134" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I134" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>244069.81</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="F135" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G135" s="16" t="n">
+        <v>0.109755</v>
+      </c>
+      <c r="H135" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I135" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>244069.81</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/Yi_Capital_US.xlsx
+++ b/assets/data/Yi_Capital_US.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="4" t="n">
-        <v>1388</v>
+        <v>2809.86</v>
       </c>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
@@ -2234,6 +2234,39 @@
         <v>138.8</v>
       </c>
       <c r="I57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Oracle Corporation</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>1421.86</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="I58" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2260,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4706,12 +4739,12 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>ETF Stock Buy Record</t>
+          <t>ETF Stock Dividend Record</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
@@ -4721,10 +4754,10 @@
         <v>-16538.54</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>-1388</v>
+        <v>61.23</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>-17926.54</v>
+        <v>-16477.31</v>
       </c>
     </row>
     <row r="103">
@@ -4735,20 +4768,188 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>ETF Stock Sell Record</t>
+          <t>ETF Stock Buy Record</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>-17926.54</v>
+        <v>-16477.31</v>
       </c>
       <c r="E103" s="9" t="n">
+        <v>-1388</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>-17865.31</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>-17865.31</v>
+      </c>
+      <c r="E104" s="9" t="n">
         <v>406.8</v>
       </c>
-      <c r="F103" s="9" t="n">
-        <v>-17519.74</v>
+      <c r="F104" s="9" t="n">
+        <v>-17458.51</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>-17458.51</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>-17094.55</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>-17094.55</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>-17050.02</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>-17050.02</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>-17018.97</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Dividend Record</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>-17018.97</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>-17017.22</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Buy Record</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>-17017.22</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>-1421.86</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>-18439.08</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>ETF Stock Sell Record</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>-18439.08</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>5630</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>-12809.08</v>
       </c>
     </row>
   </sheetData>
@@ -4762,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5074,7 +5275,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>153121.43</v>
+        <v>153121.44</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0</v>
@@ -5083,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>153121.43</v>
+        <v>153121.44</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>1513476.32</v>
@@ -5098,7 +5299,7 @@
         <v>13619.69</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>139501.74</v>
+        <v>139501.75</v>
       </c>
     </row>
     <row r="10">
@@ -5380,7 +5581,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>156915.99</v>
+        <v>156916</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>0</v>
@@ -5389,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>156915.99</v>
+        <v>156916</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>1513476.32</v>
@@ -5404,7 +5605,7 @@
         <v>13739.39</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>143176.6</v>
+        <v>143176.61</v>
       </c>
     </row>
     <row r="19">
@@ -5448,7 +5649,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>205195.01</v>
+        <v>205195.02</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
@@ -5457,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>205195.01</v>
+        <v>205195.02</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>2005476.32</v>
@@ -5472,7 +5673,7 @@
         <v>39507.2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>165687.81</v>
+        <v>165687.82</v>
       </c>
     </row>
     <row r="21">
@@ -5550,7 +5751,7 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>208407.89</v>
+        <v>208407.9</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0</v>
@@ -5559,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>208407.89</v>
+        <v>208407.9</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>2054841.55</v>
@@ -5574,7 +5775,7 @@
         <v>13000.1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>195407.79</v>
+        <v>195407.8</v>
       </c>
     </row>
     <row r="24">
@@ -5584,7 +5785,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>206929.19</v>
+        <v>206929.2</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
@@ -5593,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>206929.19</v>
+        <v>206929.2</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>2054841.55</v>
@@ -5608,7 +5809,7 @@
         <v>13000.1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>193929.09</v>
+        <v>193929.1</v>
       </c>
     </row>
     <row r="25">
@@ -5686,7 +5887,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
@@ -5695,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>2107072.57</v>
@@ -5710,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>215332.61</v>
+        <v>215332.6</v>
       </c>
     </row>
     <row r="28">
@@ -5890,7 +6091,7 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>0</v>
@@ -5899,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>2107072.57</v>
@@ -5914,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>214364.04</v>
+        <v>214364.05</v>
       </c>
     </row>
     <row r="34">
@@ -6570,7 +6771,7 @@
         </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>214364.98</v>
+        <v>214364.99</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>0</v>
@@ -6579,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>214364.98</v>
+        <v>214364.99</v>
       </c>
       <c r="F53" s="8" t="n">
         <v>2107072.57</v>
@@ -6594,7 +6795,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>227107.42</v>
+        <v>227107.43</v>
       </c>
     </row>
     <row r="54">
@@ -6638,7 +6839,7 @@
         </is>
       </c>
       <c r="B55" s="9" t="n">
-        <v>213029.51</v>
+        <v>213029.52</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>0</v>
@@ -6647,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>213029.51</v>
+        <v>213029.52</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>2107072.57</v>
@@ -6662,7 +6863,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>225771.95</v>
+        <v>225771.96</v>
       </c>
     </row>
     <row r="56">
@@ -6876,7 +7077,7 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>212156.27</v>
+        <v>212156.26</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>0</v>
@@ -6885,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>212156.27</v>
+        <v>212156.26</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>2107072.57</v>
@@ -6900,7 +7101,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>217888.28</v>
+        <v>217888.27</v>
       </c>
     </row>
     <row r="63">
@@ -7318,7 +7519,7 @@
         </is>
       </c>
       <c r="B75" s="9" t="n">
-        <v>224658.3</v>
+        <v>224658.29</v>
       </c>
       <c r="C75" s="9" t="n">
         <v>0</v>
@@ -7327,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>224658.3</v>
+        <v>224658.29</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>2107072.57</v>
@@ -7342,7 +7543,7 @@
         <v>-3745.7</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>228404</v>
+        <v>228403.99</v>
       </c>
     </row>
     <row r="76">
@@ -8066,7 +8267,7 @@
         </is>
       </c>
       <c r="B97" s="9" t="n">
-        <v>220861.6</v>
+        <v>220861.61</v>
       </c>
       <c r="C97" s="9" t="n">
         <v>0</v>
@@ -8075,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>220861.6</v>
+        <v>220861.61</v>
       </c>
       <c r="F97" s="8" t="n">
         <v>2107072.57</v>
@@ -8090,7 +8291,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>225765.16</v>
+        <v>225765.17</v>
       </c>
     </row>
     <row r="98">
@@ -9052,7 +9253,7 @@
         </is>
       </c>
       <c r="B126" s="9" t="n">
-        <v>221887.09</v>
+        <v>221948.32</v>
       </c>
       <c r="C126" s="9" t="n">
         <v>0</v>
@@ -9061,19 +9262,19 @@
         <v>0</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>221887.09</v>
+        <v>221948.32</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G126" s="16" t="n">
-        <v>0.105306</v>
+        <v>0.105335</v>
       </c>
       <c r="H126" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>-16538.54</v>
+        <v>-16477.31</v>
       </c>
       <c r="J126" s="9" t="n">
         <v>238425.63</v>
@@ -9086,7 +9287,7 @@
         </is>
       </c>
       <c r="B127" s="9" t="n">
-        <v>223453.64</v>
+        <v>223514.87</v>
       </c>
       <c r="C127" s="9" t="n">
         <v>0</v>
@@ -9095,19 +9296,19 @@
         <v>0</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>223453.64</v>
+        <v>223514.87</v>
       </c>
       <c r="F127" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G127" s="16" t="n">
-        <v>0.106049</v>
+        <v>0.106078</v>
       </c>
       <c r="H127" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17458.51</v>
       </c>
       <c r="J127" s="9" t="n">
         <v>240973.38</v>
@@ -9120,7 +9321,7 @@
         </is>
       </c>
       <c r="B128" s="9" t="n">
-        <v>221746.61</v>
+        <v>221829.33</v>
       </c>
       <c r="C128" s="9" t="n">
         <v>0</v>
@@ -9129,22 +9330,22 @@
         <v>0</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>221746.61</v>
+        <v>221829.33</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G128" s="16" t="n">
-        <v>0.105239</v>
+        <v>0.105278</v>
       </c>
       <c r="H128" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17050.02</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>239266.35</v>
+        <v>238879.35</v>
       </c>
     </row>
     <row r="129">
@@ -9154,7 +9355,7 @@
         </is>
       </c>
       <c r="B129" s="9" t="n">
-        <v>222272.13</v>
+        <v>222341.17</v>
       </c>
       <c r="C129" s="9" t="n">
         <v>0</v>
@@ -9163,22 +9364,22 @@
         <v>0</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>222272.13</v>
+        <v>222341.17</v>
       </c>
       <c r="F129" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G129" s="16" t="n">
-        <v>0.105489</v>
+        <v>0.105521</v>
       </c>
       <c r="H129" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17050.02</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>239791.87</v>
+        <v>239391.19</v>
       </c>
     </row>
     <row r="130">
@@ -9188,7 +9389,7 @@
         </is>
       </c>
       <c r="B130" s="9" t="n">
-        <v>223492</v>
+        <v>223618.37</v>
       </c>
       <c r="C130" s="9" t="n">
         <v>0</v>
@@ -9197,22 +9398,22 @@
         <v>0</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>223492</v>
+        <v>223618.37</v>
       </c>
       <c r="F130" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G130" s="16" t="n">
-        <v>0.106068</v>
+        <v>0.106128</v>
       </c>
       <c r="H130" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17018.97</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>241011.74</v>
+        <v>240637.34</v>
       </c>
     </row>
     <row r="131">
@@ -9222,7 +9423,7 @@
         </is>
       </c>
       <c r="B131" s="9" t="n">
-        <v>225633.76</v>
+        <v>225771.6</v>
       </c>
       <c r="C131" s="9" t="n">
         <v>0</v>
@@ -9231,22 +9432,22 @@
         <v>0</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>225633.76</v>
+        <v>225771.6</v>
       </c>
       <c r="F131" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G131" s="16" t="n">
-        <v>0.107084</v>
+        <v>0.107149</v>
       </c>
       <c r="H131" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-17017.22</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>243153.5</v>
+        <v>242788.82</v>
       </c>
     </row>
     <row r="132">
@@ -9256,7 +9457,7 @@
         </is>
       </c>
       <c r="B132" s="9" t="n">
-        <v>225633.76</v>
+        <v>223868.53</v>
       </c>
       <c r="C132" s="9" t="n">
         <v>0</v>
@@ -9265,22 +9466,124 @@
         <v>0</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>225633.76</v>
+        <v>223868.53</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G132" s="16" t="n">
-        <v>0.107084</v>
+        <v>0.106246</v>
       </c>
       <c r="H132" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>-17519.74</v>
+        <v>-18439.08</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>243153.5</v>
+        <v>242307.61</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="n">
+        <v>228347.57</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>228347.57</v>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G133" s="16" t="n">
+        <v>0.108372</v>
+      </c>
+      <c r="H133" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I133" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>241156.65</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>231260.73</v>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G134" s="16" t="n">
+        <v>0.109755</v>
+      </c>
+      <c r="H134" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I134" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>244069.81</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="n">
+        <v>230555.13</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>230555.13</v>
+      </c>
+      <c r="F135" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G135" s="16" t="n">
+        <v>0.10942</v>
+      </c>
+      <c r="H135" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I135" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>243364.21</v>
       </c>
     </row>
   </sheetData>
@@ -9294,7 +9597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10424,7 +10727,7 @@
       </c>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="4" t="n">
-        <v>406.8</v>
+        <v>6400.76</v>
       </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
@@ -10509,6 +10812,72 @@
         <v>20.34</v>
       </c>
       <c r="I42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>MBGL</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Mobility Global Inc.</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>PayPal Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>5630</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I44" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10537,7 +10906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11882,11 +12251,195 @@
       </c>
       <c r="H49" s="7" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2026/07/01-2026/07/31</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Total Dividend Amount:</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="4" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Trade No.</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Stock/ETF Name</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Div Per Share (USD)</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>PBR-A</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras (Preferred ADR)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>0.10205</v>
+      </c>
+      <c r="H53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>iShares 20+ Year Treasury Bond ETF</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="H54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>SGOV</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>iShares 0-3 Month Treasury Bond ETF</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="H55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>PGR</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>The Progressive Corporation</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H56" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="D32:E32"/>
@@ -12057,7 +12610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12085,7 +12638,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -12103,7 +12656,7 @@
       </c>
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="4" t="n">
-        <v>240276.88</v>
+        <v>243363.9</v>
       </c>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
@@ -12203,13 +12756,13 @@
         <v>20</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>428.1900024414062</v>
+        <v>432.3900146484375</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>8563.800048828125</v>
+        <v>8647.80029296875</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>0.03564138202803051</v>
+        <v>0.03553444227620745</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>6893.1</v>
@@ -12224,13 +12777,13 @@
         <v>6893.1</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>1734.120048828125</v>
+        <v>1818.12029296875</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>0.2423728146738223</v>
+        <v>0.2545589492345605</v>
       </c>
       <c r="N3" s="15" t="n">
-        <v>0.2515733195265011</v>
+        <v>0.2637594540872393</v>
       </c>
       <c r="O3" s="7" t="n"/>
     </row>
@@ -12252,13 +12805,13 @@
         <v>150</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>74.33000183105469</v>
+        <v>72.05000305175781</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>11149.5002746582</v>
+        <v>10807.50045776367</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.04640271800426989</v>
+        <v>0.04440880780731467</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>12219</v>
@@ -12273,13 +12826,13 @@
         <v>12219</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>-1069.499725341795</v>
+        <v>-1411.499542236326</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>-0.0875275984402812</v>
+        <v>-0.1155167806069504</v>
       </c>
       <c r="N4" s="15" t="n">
-        <v>-0.08752759844028114</v>
+        <v>-0.1155167806069504</v>
       </c>
       <c r="O4" s="7" t="n"/>
     </row>
@@ -12301,13 +12854,13 @@
         <v>20</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>377.489990234375</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>7549.7998046875</v>
+        <v>7376.599731445312</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0.03142124962514032</v>
+        <v>0.03031098643256771</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>22085.17</v>
@@ -12322,13 +12875,13 @@
         <v>9410.169999999998</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>-1860.370195312498</v>
+        <v>-2033.570268554686</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>-0.1976978306781385</v>
+        <v>-0.2161034570634416</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>-0.08423617274906638</v>
+        <v>-0.09207854268519038</v>
       </c>
       <c r="O5" s="7" t="n"/>
     </row>
@@ -12350,13 +12903,13 @@
         <v>600</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>14.98999977111816</v>
+        <v>16</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>8993.999862670898</v>
+        <v>9600</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.03743181569370865</v>
+        <v>0.03944710033705958</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>11165</v>
@@ -12365,19 +12918,19 @@
         <v>6936</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>229.77</v>
+        <v>291</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>4229</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>4994.769862670899</v>
+        <v>5662</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>1.126743878616907</v>
+        <v>1.270040198628518</v>
       </c>
       <c r="N6" s="15" t="n">
-        <v>0.4473595936113658</v>
+        <v>0.5071204657411554</v>
       </c>
       <c r="O6" s="7" t="n"/>
     </row>
@@ -12399,13 +12952,13 @@
         <v>107</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>221.5399932861328</v>
+        <v>235.25</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>23704.77928161621</v>
+        <v>25171.75</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0.09865609769600341</v>
+        <v>0.1034325570738937</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>28073.97</v>
@@ -12420,13 +12973,13 @@
         <v>28073.97</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>-4369.19071838379</v>
+        <v>-2902.220000000001</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>-0.1556313808978136</v>
+        <v>-0.1033776127850818</v>
       </c>
       <c r="N7" s="15" t="n">
-        <v>-0.1556313808978135</v>
+        <v>-0.1033776127850817</v>
       </c>
       <c r="O7" s="7" t="n"/>
     </row>
@@ -12448,13 +13001,13 @@
         <v>43</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>388.8399963378906</v>
+        <v>392.5400085449219</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>16720.1198425293</v>
+        <v>16879.22036743164</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.06958688613281989</v>
+        <v>0.06935794785889746</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>17698.7</v>
@@ -12469,13 +13022,13 @@
         <v>17698.7</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>-915.9701574707033</v>
+        <v>-756.8696325683595</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>-0.05529107547281454</v>
+        <v>-0.04630168501462587</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>-0.05175352751731501</v>
+        <v>-0.04276413705912635</v>
       </c>
       <c r="O8" s="7" t="n"/>
     </row>
@@ -12497,13 +13050,13 @@
         <v>500</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>27.05999946594238</v>
+        <v>28.52000045776367</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>13529.99973297119</v>
+        <v>14260.00022888184</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0.0563100360321894</v>
+        <v>0.05859538123283274</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>12425</v>
@@ -12518,13 +13071,13 @@
         <v>12425</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1104.999732971191</v>
+        <v>1835.000228881836</v>
       </c>
       <c r="M9" s="15" t="n">
-        <v>0.08893358011840569</v>
+        <v>0.1476861351212745</v>
       </c>
       <c r="N9" s="15" t="n">
-        <v>0.08893358011840574</v>
+        <v>0.1476861351212745</v>
       </c>
       <c r="O9" s="7" t="n"/>
     </row>
@@ -12546,13 +13099,13 @@
         <v>25</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>234.3999938964844</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5859.999847412109</v>
+        <v>5192.250061035156</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0.02438852986465931</v>
+        <v>0.02133533428466224</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>5210</v>
@@ -12561,19 +13114,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>5210</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>651.7498474121094</v>
+        <v>-14.24993896484375</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>0.1247600474879288</v>
+        <v>-0.00340689807386639</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>0.1250959400023243</v>
+        <v>-0.002735113045075576</v>
       </c>
       <c r="O10" s="7" t="n"/>
     </row>
@@ -12595,13 +13148,13 @@
         <v>430</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>37.09999847412109</v>
+        <v>38.34500122070312</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>15952.99934387207</v>
+        <v>16488.35052490234</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0.06639423396926115</v>
+        <v>0.06775183516129497</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>17180.9</v>
@@ -12616,13 +13169,13 @@
         <v>17180.9</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>-1087.390656127931</v>
+        <v>-552.0394750976593</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.0714689367918987</v>
+        <v>-0.04030926640034335</v>
       </c>
       <c r="N11" s="15" t="n">
-        <v>-0.06329066906436397</v>
+        <v>-0.03213099867280871</v>
       </c>
       <c r="O11" s="7" t="n"/>
     </row>
@@ -12644,13 +13197,13 @@
         <v>200</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>23.40999984741211</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4681.999969482422</v>
+        <v>4779.999923706055</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>0.01948585308111966</v>
+        <v>0.01964136839599686</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>5947</v>
@@ -12665,13 +13218,13 @@
         <v>5947</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>-1218.800030517578</v>
+        <v>-1120.800076293945</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.2127122970434804</v>
+        <v>-0.1962334078180503</v>
       </c>
       <c r="N12" s="15" t="n">
-        <v>-0.2049436742084376</v>
+        <v>-0.1884647849830075</v>
       </c>
       <c r="O12" s="7" t="n"/>
     </row>
@@ -12693,13 +13246,13 @@
         <v>120</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>128.2200012207031</v>
+        <v>125.9100036621094</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>15386.40014648438</v>
+        <v>15109.20043945312</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0.06403612444595044</v>
+        <v>0.0620848068487346</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>14520</v>
@@ -12714,13 +13267,13 @@
         <v>14520</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1070.880146484375</v>
+        <v>793.6804394531246</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>0.05966943157605888</v>
+        <v>0.04057854266206095</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.07375207620415802</v>
+        <v>0.0546611872901601</v>
       </c>
       <c r="O13" s="7" t="n"/>
     </row>
@@ -12739,19 +13292,19 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>141.6000061035156</v>
+        <v>127.2799987792969</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>5522.400238037109</v>
+        <v>7636.799926757812</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0.02298348577422718</v>
+        <v>0.0313801680171734</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>17927.57</v>
+        <v>20737.43</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>15703.6</v>
@@ -12760,16 +13313,16 @@
         <v>28</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2223.969999999999</v>
+        <v>5033.83</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3326.430238037108</v>
+        <v>2630.969926757811</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>1.483127127630818</v>
+        <v>0.5170953184270849</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.1855483056564335</v>
+        <v>0.1268705874719196</v>
       </c>
       <c r="O14" s="7" t="n"/>
     </row>
@@ -12791,13 +13344,13 @@
         <v>40</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>352.2000122070312</v>
+        <v>358.7200012207031</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>14088.00048828125</v>
+        <v>14348.80004882812</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0.0586323599980154</v>
+        <v>0.05896026617109671</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>12988</v>
@@ -12812,13 +13365,13 @@
         <v>12988</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1118.76048828125</v>
+        <v>1379.560048828125</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>0.0846936008839891</v>
+        <v>0.1047736409630525</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.086138011108812</v>
+        <v>0.1062180511878754</v>
       </c>
       <c r="O15" s="7" t="n"/>
     </row>
@@ -12840,13 +13393,13 @@
         <v>200</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>84.55000305175781</v>
+        <v>84.55500030517578</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>16910.00061035156</v>
+        <v>16911.00006103516</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0.07037714430642766</v>
+        <v>0.06948853293829942</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>17734</v>
@@ -12855,19 +13408,19 @@
         <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>136.57</v>
+        <v>181.1</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>17734</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>-687.4293896484378</v>
+        <v>-641.8999389648452</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.04646438421385124</v>
+        <v>-0.04640802633161408</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.03876335793664361</v>
+        <v>-0.03619600422718198</v>
       </c>
       <c r="O16" s="7" t="n"/>
     </row>
@@ -12889,13 +13442,13 @@
         <v>150</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>100.4599990844727</v>
+        <v>100.5749969482422</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>15068.9998626709</v>
+        <v>15086.24954223633</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0.06271514722711061</v>
+        <v>0.06199049993776204</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>16683</v>
@@ -12904,19 +13457,19 @@
         <v>1607.52</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>93.29000000000001</v>
+        <v>124.34</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>15075.48</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>86.80986267089975</v>
+        <v>135.1095422363287</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>-0.0004298461693491978</v>
+        <v>0.0007143747486865589</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>0.005203492337762977</v>
+        <v>0.008098635871026117</v>
       </c>
       <c r="O17" s="7" t="n"/>
     </row>
@@ -12938,13 +13491,13 @@
         <v>150</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>49.63999938964844</v>
+        <v>50.5099983215332</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>7445.999908447266</v>
+        <v>7576.49974822998</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0.03098924844163833</v>
+        <v>0.03113239018459736</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>5769</v>
@@ -12959,13 +13512,13 @@
         <v>5769</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1808.059908447266</v>
+        <v>1938.559748229981</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.2906916117953312</v>
+        <v>0.3133124888594176</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.3134095871810134</v>
+        <v>0.3360304642450998</v>
       </c>
       <c r="O18" s="7" t="n"/>
     </row>
@@ -12984,37 +13537,37 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>45.65000152587891</v>
+        <v>56.68999862670898</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>18260.00061035156</v>
+        <v>17006.9995880127</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0.07599566242496143</v>
+        <v>0.06988300199798622</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>18236.4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>39.2</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>18236.4</v>
+        <v>12606.4</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>62.80061035156177</v>
+        <v>4439.799588012695</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>0.001294148535432545</v>
+        <v>0.3490766267937471</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.003443695595159229</v>
+        <v>0.2434581160762373</v>
       </c>
       <c r="O19" s="7" t="n"/>
     </row>
@@ -13036,13 +13589,13 @@
         <v>40</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>196.9299926757812</v>
+        <v>204.4149932861328</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>7877.19970703125</v>
+        <v>8176.599731445312</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0.03278384390908443</v>
+        <v>0.03359824479398934</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>8635</v>
@@ -13057,13 +13610,13 @@
         <v>8635</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-757.80029296875</v>
+        <v>-458.4002685546875</v>
       </c>
       <c r="M20" s="15" t="n">
-        <v>-0.08775915378908512</v>
+        <v>-0.05308630788126086</v>
       </c>
       <c r="N20" s="15" t="n">
-        <v>-0.08775915378908512</v>
+        <v>-0.05308630788126086</v>
       </c>
       <c r="O20" s="7" t="n"/>
     </row>
@@ -13085,13 +13638,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>535.3800048828125</v>
+        <v>518.1199951171875</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>5353.800048828125</v>
+        <v>5181.199951171875</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>0.02228179450173911</v>
+        <v>0.02128992857710887</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>5069.8</v>
@@ -13106,13 +13659,13 @@
         <v>5069.8</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>284.0000488281248</v>
+        <v>111.3999511718748</v>
       </c>
       <c r="M21" s="15" t="n">
-        <v>0.05601799850647458</v>
+        <v>0.02197324375160259</v>
       </c>
       <c r="N21" s="15" t="n">
-        <v>0.05601799850647458</v>
+        <v>0.02197324375160259</v>
       </c>
       <c r="O21" s="7" t="n"/>
     </row>
@@ -13134,16 +13687,16 @@
         <v>38</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>443.4599914550781</v>
+        <v>450.7124938964844</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>16851.47967529297</v>
+        <v>17127.07476806641</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>0.07013358805906453</v>
+        <v>0.07037639967252468</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>14284.37917736824</v>
+        <v>14284.70668805384</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
@@ -13152,67 +13705,18 @@
         <v>51.6</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>14284.37917736824</v>
+        <v>14284.70668805384</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>2618.700497924729</v>
+        <v>2893.968080012561</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>0.1797138304751787</v>
+        <v>0.198979800011547</v>
       </c>
       <c r="N22" s="15" t="n">
-        <v>0.1833261680755242</v>
+        <v>0.2025920547905094</v>
       </c>
       <c r="O22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>MBGL</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Mobility Global Inc.</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>21.20000076293945</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>805.6000289916992</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>0.003352798784578661</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>729.7608226317609</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>729.7608226317609</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>75.83920635993832</v>
-      </c>
-      <c r="M23" s="15" t="n">
-        <v>0.1039233732587026</v>
-      </c>
-      <c r="N23" s="15" t="n">
-        <v>0.1039233732587025</v>
-      </c>
-      <c r="O23" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/data/Yi_Capital_US.xlsx
+++ b/assets/data/Yi_Capital_US.xlsx
@@ -4963,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>149264.12</v>
+        <v>150222.73</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>0</v>
@@ -5080,13 +5080,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>149264.12</v>
+        <v>150222.73</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>1490000</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>0.100177</v>
+        <v>0.100821</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>-0</v>
@@ -5095,7 +5095,7 @@
         <v>20973.41</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>128290.71</v>
+        <v>129249.32</v>
       </c>
     </row>
     <row r="4">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>150119.19</v>
+        <v>151078.44</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>150119.19</v>
+        <v>151078.44</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>1498735.32</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.100164</v>
+        <v>0.100804</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>-0</v>
@@ -5129,7 +5129,7 @@
         <v>13485.14</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>136634.05</v>
+        <v>137593.3</v>
       </c>
     </row>
     <row r="5">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>150551.51</v>
+        <v>151521.76</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>0</v>
@@ -5148,13 +5148,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>150551.51</v>
+        <v>151521.76</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>1498735.32</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.100452</v>
+        <v>0.1011</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>-0</v>
@@ -5163,7 +5163,7 @@
         <v>13485.14</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>137066.37</v>
+        <v>138036.62</v>
       </c>
     </row>
     <row r="6">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>151244.04</v>
+        <v>152224.72</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>0</v>
@@ -5182,13 +5182,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>151244.04</v>
+        <v>152224.72</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>1498735.32</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.100914</v>
+        <v>0.101569</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>-0</v>
@@ -5197,7 +5197,7 @@
         <v>13485.14</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>137758.9</v>
+        <v>138739.58</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>151465.78</v>
+        <v>152446.31</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>0</v>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>151465.78</v>
+        <v>152446.31</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>1498735.32</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.101062</v>
+        <v>0.101717</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>-0</v>
@@ -5231,7 +5231,7 @@
         <v>26160.14</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>125305.64</v>
+        <v>126286.17</v>
       </c>
     </row>
     <row r="8">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>153411.07</v>
+        <v>154396.15</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>0</v>
@@ -5250,13 +5250,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>153411.07</v>
+        <v>154396.15</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.101363</v>
+        <v>0.102014</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>-0</v>
@@ -5265,7 +5265,7 @@
         <v>27755.54</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>125655.53</v>
+        <v>126640.61</v>
       </c>
     </row>
     <row r="9">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>153121.44</v>
+        <v>154498.27</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>0</v>
@@ -5284,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>153121.44</v>
+        <v>154498.27</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.101172</v>
+        <v>0.102082</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>-0</v>
@@ -5299,7 +5299,7 @@
         <v>13619.69</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>139501.75</v>
+        <v>140878.58</v>
       </c>
     </row>
     <row r="10">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>153368.67</v>
+        <v>154752.15</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>0</v>
@@ -5318,13 +5318,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>153368.67</v>
+        <v>154752.15</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.101335</v>
+        <v>0.102249</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>-0</v>
@@ -5333,7 +5333,7 @@
         <v>13619.69</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>139748.98</v>
+        <v>141132.46</v>
       </c>
     </row>
     <row r="11">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>153834.71</v>
+        <v>155211.36</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>0</v>
@@ -5352,13 +5352,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>153834.71</v>
+        <v>155211.36</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.101643</v>
+        <v>0.102553</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>-0</v>
@@ -5367,7 +5367,7 @@
         <v>13619.69</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>140215.02</v>
+        <v>141591.67</v>
       </c>
     </row>
     <row r="12">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>152521.84</v>
+        <v>153891.83</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>0</v>
@@ -5386,13 +5386,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>152521.84</v>
+        <v>153891.83</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.100776</v>
+        <v>0.101681</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>-0</v>
@@ -5401,7 +5401,7 @@
         <v>13619.69</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>138902.15</v>
+        <v>140272.14</v>
       </c>
     </row>
     <row r="13">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>154920.8</v>
+        <v>156313.9</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>0</v>
@@ -5420,13 +5420,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>154920.8</v>
+        <v>156313.9</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.102361</v>
+        <v>0.103281</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>-0</v>
@@ -5435,7 +5435,7 @@
         <v>13619.69</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>141301.11</v>
+        <v>142694.21</v>
       </c>
     </row>
     <row r="14">
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>155385.11</v>
+        <v>156786.22</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>0</v>
@@ -5454,13 +5454,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>155385.11</v>
+        <v>156786.22</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.102668</v>
+        <v>0.103593</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>-0</v>
@@ -5469,7 +5469,7 @@
         <v>5473.79</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>149911.32</v>
+        <v>151312.43</v>
       </c>
     </row>
     <row r="15">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>156251.29</v>
+        <v>157555.4</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>0</v>
@@ -5488,13 +5488,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>156251.29</v>
+        <v>157555.4</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0.10324</v>
+        <v>0.104102</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>-0</v>
@@ -5503,7 +5503,7 @@
         <v>5473.79</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>150777.5</v>
+        <v>152081.61</v>
       </c>
     </row>
     <row r="16">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>156285.19</v>
+        <v>157592.61</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>0</v>
@@ -5522,13 +5522,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>156285.19</v>
+        <v>157592.61</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.103262</v>
+        <v>0.104126</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>-0</v>
@@ -5537,7 +5537,7 @@
         <v>5473.79</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>150811.4</v>
+        <v>152118.82</v>
       </c>
     </row>
     <row r="17">
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>156253.25</v>
+        <v>157512.09</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>0</v>
@@ -5556,13 +5556,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>156253.25</v>
+        <v>157512.09</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.103241</v>
+        <v>0.104073</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>-0</v>
@@ -5571,7 +5571,7 @@
         <v>13739.39</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>142513.86</v>
+        <v>143772.7</v>
       </c>
     </row>
     <row r="18">
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>156916</v>
+        <v>158172.65</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>0</v>
@@ -5590,13 +5590,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>156916</v>
+        <v>158172.65</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.103679</v>
+        <v>0.104509</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>-0</v>
@@ -5605,7 +5605,7 @@
         <v>13739.39</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>143176.61</v>
+        <v>144433.26</v>
       </c>
     </row>
     <row r="19">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>155929.19</v>
+        <v>157175.87</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>155929.19</v>
+        <v>157175.87</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>1513476.32</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>0.103027</v>
+        <v>0.103851</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>-0</v>
@@ -5639,7 +5639,7 @@
         <v>27249.8</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>128679.39</v>
+        <v>129926.07</v>
       </c>
     </row>
     <row r="20">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>205195.02</v>
+        <v>206679.41</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
@@ -5658,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>205195.02</v>
+        <v>206679.41</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>2005476.32</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>0.102317</v>
+        <v>0.103058</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>-0</v>
@@ -5673,7 +5673,7 @@
         <v>39507.2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>165687.82</v>
+        <v>167172.21</v>
       </c>
     </row>
     <row r="21">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>204602.42</v>
+        <v>205994.97</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>0</v>
@@ -5692,13 +5692,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>204602.42</v>
+        <v>205994.97</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>2005476.32</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0.102022</v>
+        <v>0.102716</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>39507.2</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>165095.22</v>
+        <v>166487.77</v>
       </c>
     </row>
     <row r="22">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>208488.16</v>
+        <v>210488.81</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>208488.16</v>
+        <v>210488.81</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>2054841.55</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.101462</v>
+        <v>0.102436</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>-0</v>
@@ -5741,7 +5741,7 @@
         <v>13000.1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>195488.06</v>
+        <v>197488.71</v>
       </c>
     </row>
     <row r="23">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>208407.9</v>
+        <v>210432.09</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>0</v>
@@ -5760,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>208407.9</v>
+        <v>210432.09</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>2054841.55</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>0.101423</v>
+        <v>0.102408</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>-0</v>
@@ -5775,7 +5775,7 @@
         <v>13000.1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>195407.8</v>
+        <v>197431.99</v>
       </c>
     </row>
     <row r="24">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>206929.2</v>
+        <v>208951.23</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
@@ -5794,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>206929.2</v>
+        <v>208951.23</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>2054841.55</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>0.100703</v>
+        <v>0.101687</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>-0</v>
@@ -5809,7 +5809,7 @@
         <v>13000.1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>193929.1</v>
+        <v>195951.13</v>
       </c>
     </row>
     <row r="25">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>208307.85</v>
+        <v>210356.13</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>0</v>
@@ -5828,13 +5828,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>208307.85</v>
+        <v>210356.13</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>2054841.55</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>0.101374</v>
+        <v>0.102371</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>-0</v>
@@ -5843,7 +5843,7 @@
         <v>13059.23</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>195248.62</v>
+        <v>197296.9</v>
       </c>
     </row>
     <row r="26">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>210214.15</v>
+        <v>211896.98</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>0</v>
@@ -5862,13 +5862,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>210214.15</v>
+        <v>211896.98</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>2054841.55</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>0.102302</v>
+        <v>0.103121</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>-0</v>
@@ -5877,7 +5877,7 @@
         <v>36153.78</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>174060.37</v>
+        <v>175743.2</v>
       </c>
     </row>
     <row r="27">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>215332.6</v>
+        <v>217945.99</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>0</v>
@@ -5896,13 +5896,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>215332.6</v>
+        <v>217945.99</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>0.102195</v>
+        <v>0.103435</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>-0</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>215332.6</v>
+        <v>217945.99</v>
       </c>
     </row>
     <row r="28">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>214482.65</v>
+        <v>217081.91</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>0</v>
@@ -5930,13 +5930,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>214482.65</v>
+        <v>217081.91</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>0.101792</v>
+        <v>0.103025</v>
       </c>
       <c r="H28" s="9" t="n">
         <v>-0</v>
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>214482.65</v>
+        <v>217081.91</v>
       </c>
     </row>
     <row r="29">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>213739.8</v>
+        <v>216344.27</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>0</v>
@@ -5964,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>213739.8</v>
+        <v>216344.27</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>0.101439</v>
+        <v>0.102675</v>
       </c>
       <c r="H29" s="9" t="n">
         <v>-0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>213739.8</v>
+        <v>216344.27</v>
       </c>
     </row>
     <row r="30">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>214682.67</v>
+        <v>217192.27</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>214682.67</v>
+        <v>217192.27</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>0.101887</v>
+        <v>0.103078</v>
       </c>
       <c r="H30" s="9" t="n">
         <v>-0</v>
@@ -6013,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>214682.67</v>
+        <v>217192.27</v>
       </c>
     </row>
     <row r="31">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>212741.95</v>
+        <v>215229.43</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>0</v>
@@ -6032,13 +6032,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>212741.95</v>
+        <v>215229.43</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0.100966</v>
+        <v>0.102146</v>
       </c>
       <c r="H31" s="9" t="n">
         <v>-0</v>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>212741.95</v>
+        <v>215229.43</v>
       </c>
     </row>
     <row r="32">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>214436.43</v>
+        <v>216948.73</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>0</v>
@@ -6066,13 +6066,13 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>214436.43</v>
+        <v>216948.73</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.10177</v>
+        <v>0.102962</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>-0</v>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>214436.43</v>
+        <v>216948.73</v>
       </c>
     </row>
     <row r="33">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>214364.05</v>
+        <v>216832.21</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>0</v>
@@ -6100,13 +6100,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>214364.05</v>
+        <v>216832.21</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0.101735</v>
+        <v>0.102907</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>214364.05</v>
+        <v>216832.21</v>
       </c>
     </row>
     <row r="34">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>214092.99</v>
+        <v>216557.7</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>0</v>
@@ -6134,13 +6134,13 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>214092.99</v>
+        <v>216557.7</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>0.101607</v>
+        <v>0.102777</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>-0</v>
@@ -6149,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>214092.99</v>
+        <v>216557.7</v>
       </c>
     </row>
     <row r="35">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>211259.03</v>
+        <v>213698.51</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>211259.03</v>
+        <v>213698.51</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>0.100262</v>
+        <v>0.10142</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>-0</v>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>211259.03</v>
+        <v>213698.51</v>
       </c>
     </row>
     <row r="36">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>213535.25</v>
+        <v>216013.65</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>0</v>
@@ -6202,13 +6202,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>213535.25</v>
+        <v>216013.65</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>0.101342</v>
+        <v>0.102518</v>
       </c>
       <c r="H36" s="9" t="n">
         <v>-0</v>
@@ -6217,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>213535.25</v>
+        <v>216013.65</v>
       </c>
     </row>
     <row r="37">
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>215183.4</v>
+        <v>217637.45</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>0</v>
@@ -6236,13 +6236,13 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>215183.4</v>
+        <v>217637.45</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>0.102124</v>
+        <v>0.103289</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>-0</v>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>215183.4</v>
+        <v>217637.45</v>
       </c>
     </row>
     <row r="38">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>216819.89</v>
+        <v>219307.71</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>0</v>
@@ -6270,13 +6270,13 @@
         <v>0</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>216819.89</v>
+        <v>219307.71</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>0.102901</v>
+        <v>0.104082</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>-0</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>216819.89</v>
+        <v>219307.71</v>
       </c>
     </row>
     <row r="39">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>217434.09</v>
+        <v>219934.68</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>0</v>
@@ -6304,13 +6304,13 @@
         <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>217434.09</v>
+        <v>219934.68</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>0.103193</v>
+        <v>0.104379</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>-0</v>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>217434.09</v>
+        <v>219934.68</v>
       </c>
     </row>
     <row r="40">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>218887.31</v>
+        <v>220913.95</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>218887.31</v>
+        <v>220913.95</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>0.103882</v>
+        <v>0.104844</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>-0</v>
@@ -6353,7 +6353,7 @@
         <v>43769.55</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>175117.76</v>
+        <v>177144.4</v>
       </c>
     </row>
     <row r="41">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="B41" s="9" t="n">
-        <v>218860.59</v>
+        <v>220879.14</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>0</v>
@@ -6372,13 +6372,13 @@
         <v>0</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>218860.59</v>
+        <v>220879.14</v>
       </c>
       <c r="F41" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>0.10387</v>
+        <v>0.104827</v>
       </c>
       <c r="H41" s="9" t="n">
         <v>-0</v>
@@ -6387,7 +6387,7 @@
         <v>43769.55</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>175091.04</v>
+        <v>177109.59</v>
       </c>
     </row>
     <row r="42">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>219752.17</v>
+        <v>221777.29</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>0</v>
@@ -6406,13 +6406,13 @@
         <v>0</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>219752.17</v>
+        <v>221777.29</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.104293</v>
+        <v>0.105254</v>
       </c>
       <c r="H42" s="9" t="n">
         <v>-0</v>
@@ -6421,7 +6421,7 @@
         <v>43769.55</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>175982.62</v>
+        <v>178007.74</v>
       </c>
     </row>
     <row r="43">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>220403.53</v>
+        <v>222708.25</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>0</v>
@@ -6440,13 +6440,13 @@
         <v>0</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>220403.53</v>
+        <v>222708.25</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>0.104602</v>
+        <v>0.105696</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>-0</v>
@@ -6455,7 +6455,7 @@
         <v>26035.55</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>194367.98</v>
+        <v>196672.7</v>
       </c>
     </row>
     <row r="44">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>221262.31</v>
+        <v>223983.81</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>0</v>
@@ -6474,13 +6474,13 @@
         <v>0</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>221262.31</v>
+        <v>223983.81</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.105009</v>
+        <v>0.106301</v>
       </c>
       <c r="H44" s="9" t="n">
         <v>-0</v>
@@ -6489,7 +6489,7 @@
         <v>3659.51</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>217602.8</v>
+        <v>220324.3</v>
       </c>
     </row>
     <row r="45">
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="B45" s="9" t="n">
-        <v>220747.9</v>
+        <v>223415.67</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>220747.9</v>
+        <v>223415.67</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.104765</v>
+        <v>0.106031</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>-0</v>
@@ -6523,7 +6523,7 @@
         <v>3756.26</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>216991.64</v>
+        <v>219659.41</v>
       </c>
     </row>
     <row r="46">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>218614.38</v>
+        <v>221243.43</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>0</v>
@@ -6542,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>218614.38</v>
+        <v>221243.43</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>0.103753</v>
+        <v>0.105</v>
       </c>
       <c r="H46" s="9" t="n">
         <v>-0</v>
@@ -6557,7 +6557,7 @@
         <v>3756.26</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>214858.12</v>
+        <v>217487.17</v>
       </c>
     </row>
     <row r="47">
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>220498.46</v>
+        <v>223101.63</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>0</v>
@@ -6576,13 +6576,13 @@
         <v>0</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>220498.46</v>
+        <v>223101.63</v>
       </c>
       <c r="F47" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>0.104647</v>
+        <v>0.105882</v>
       </c>
       <c r="H47" s="9" t="n">
         <v>-0</v>
@@ -6591,7 +6591,7 @@
         <v>7156.26</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>213342.2</v>
+        <v>215945.37</v>
       </c>
     </row>
     <row r="48">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>218555.13</v>
+        <v>221100.52</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>0</v>
@@ -6610,13 +6610,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>218555.13</v>
+        <v>221100.52</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>0.103725</v>
+        <v>0.104933</v>
       </c>
       <c r="H48" s="9" t="n">
         <v>-0</v>
@@ -6625,7 +6625,7 @@
         <v>8789.58</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>209765.55</v>
+        <v>212310.94</v>
       </c>
     </row>
     <row r="49">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>215734.56</v>
+        <v>218335.46</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>0</v>
@@ -6644,13 +6644,13 @@
         <v>0</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>215734.56</v>
+        <v>218335.46</v>
       </c>
       <c r="F49" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>0.102386</v>
+        <v>0.10362</v>
       </c>
       <c r="H49" s="9" t="n">
         <v>-0</v>
@@ -6659,7 +6659,7 @@
         <v>-9411.6</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>225146.16</v>
+        <v>227747.06</v>
       </c>
     </row>
     <row r="50">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="B50" s="9" t="n">
-        <v>217771.85</v>
+        <v>220398.74</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>0</v>
@@ -6678,13 +6678,13 @@
         <v>0</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>217771.85</v>
+        <v>220398.74</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>0.103353</v>
+        <v>0.1046</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>-0</v>
@@ -6693,7 +6693,7 @@
         <v>-11876.6</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>229648.45</v>
+        <v>232275.34</v>
       </c>
     </row>
     <row r="51">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="B51" s="9" t="n">
-        <v>219418.96</v>
+        <v>221959.02</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>0</v>
@@ -6712,13 +6712,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>219418.96</v>
+        <v>221959.02</v>
       </c>
       <c r="F51" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>0.104135</v>
+        <v>0.10534</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>-0</v>
@@ -6727,7 +6727,7 @@
         <v>-4825.58</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>224244.54</v>
+        <v>226784.6</v>
       </c>
     </row>
     <row r="52">
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>215143.4</v>
+        <v>217895</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>0</v>
@@ -6746,13 +6746,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>215143.4</v>
+        <v>217895</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G52" s="16" t="n">
-        <v>0.102105</v>
+        <v>0.103411</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>-0</v>
@@ -6761,7 +6761,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>227885.84</v>
+        <v>230637.44</v>
       </c>
     </row>
     <row r="53">
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>214364.99</v>
+        <v>217115.67</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>0</v>
@@ -6780,13 +6780,13 @@
         <v>0</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>214364.99</v>
+        <v>217115.67</v>
       </c>
       <c r="F53" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>0.101736</v>
+        <v>0.103041</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>-0</v>
@@ -6795,7 +6795,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>227107.43</v>
+        <v>229858.11</v>
       </c>
     </row>
     <row r="54">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>211844.77</v>
+        <v>214561.96</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>0</v>
@@ -6814,13 +6814,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>211844.77</v>
+        <v>214561.96</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>0.10054</v>
+        <v>0.101829</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>-0</v>
@@ -6829,7 +6829,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>224587.21</v>
+        <v>227304.4</v>
       </c>
     </row>
     <row r="55">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="B55" s="9" t="n">
-        <v>213029.52</v>
+        <v>215771.3</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>0</v>
@@ -6848,13 +6848,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>213029.52</v>
+        <v>215771.3</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>0.101102</v>
+        <v>0.102403</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>-0</v>
@@ -6863,7 +6863,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>225771.96</v>
+        <v>228513.74</v>
       </c>
     </row>
     <row r="56">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>210102.87</v>
+        <v>212799.32</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>0</v>
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>210102.87</v>
+        <v>212799.32</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G56" s="16" t="n">
-        <v>0.099713</v>
+        <v>0.100993</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>-0</v>
@@ -6897,7 +6897,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>222845.31</v>
+        <v>225541.76</v>
       </c>
     </row>
     <row r="57">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="B57" s="9" t="n">
-        <v>210156.92</v>
+        <v>212841.37</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>0</v>
@@ -6916,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>210156.92</v>
+        <v>212841.37</v>
       </c>
       <c r="F57" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>0.09973899999999999</v>
+        <v>0.101013</v>
       </c>
       <c r="H57" s="9" t="n">
         <v>-0</v>
@@ -6931,7 +6931,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>222899.36</v>
+        <v>225583.81</v>
       </c>
     </row>
     <row r="58">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>209875.21</v>
+        <v>212566.43</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>0</v>
@@ -6950,13 +6950,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>209875.21</v>
+        <v>212566.43</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G58" s="16" t="n">
-        <v>0.099605</v>
+        <v>0.100882</v>
       </c>
       <c r="H58" s="9" t="n">
         <v>-0</v>
@@ -6965,7 +6965,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>222617.65</v>
+        <v>225308.87</v>
       </c>
     </row>
     <row r="59">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B59" s="9" t="n">
-        <v>207664.81</v>
+        <v>210338.67</v>
       </c>
       <c r="C59" s="9" t="n">
         <v>0</v>
@@ -6984,13 +6984,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>207664.81</v>
+        <v>210338.67</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G59" s="16" t="n">
-        <v>0.098556</v>
+        <v>0.099825</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>-0</v>
@@ -6999,7 +6999,7 @@
         <v>-12742.44</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>220407.25</v>
+        <v>223081.11</v>
       </c>
     </row>
     <row r="60">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>210662.18</v>
+        <v>213077.38</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>0</v>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>210662.18</v>
+        <v>213077.38</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0.099979</v>
+        <v>0.101125</v>
       </c>
       <c r="H60" s="9" t="n">
         <v>-0</v>
@@ -7033,7 +7033,7 @@
         <v>-5792.88</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>216455.06</v>
+        <v>218870.26</v>
       </c>
     </row>
     <row r="61">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="B61" s="9" t="n">
-        <v>213329.54</v>
+        <v>215766.58</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>0</v>
@@ -7052,13 +7052,13 @@
         <v>0</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>213329.54</v>
+        <v>215766.58</v>
       </c>
       <c r="F61" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G61" s="16" t="n">
-        <v>0.101245</v>
+        <v>0.102401</v>
       </c>
       <c r="H61" s="9" t="n">
         <v>-0</v>
@@ -7067,7 +7067,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>219061.55</v>
+        <v>221498.59</v>
       </c>
     </row>
     <row r="62">
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>212156.26</v>
+        <v>214406.65</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>0</v>
@@ -7086,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>212156.26</v>
+        <v>214406.65</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0.100688</v>
+        <v>0.101756</v>
       </c>
       <c r="H62" s="9" t="n">
         <v>-0</v>
@@ -7101,7 +7101,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>217888.27</v>
+        <v>220138.66</v>
       </c>
     </row>
     <row r="63">
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="B63" s="9" t="n">
-        <v>213949.26</v>
+        <v>216220.44</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>0</v>
@@ -7120,13 +7120,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>213949.26</v>
+        <v>216220.44</v>
       </c>
       <c r="F63" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G63" s="16" t="n">
-        <v>0.101539</v>
+        <v>0.102617</v>
       </c>
       <c r="H63" s="9" t="n">
         <v>-0</v>
@@ -7135,7 +7135,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>219681.27</v>
+        <v>221952.45</v>
       </c>
     </row>
     <row r="64">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>214485.24</v>
+        <v>216766.73</v>
       </c>
       <c r="C64" s="9" t="n">
         <v>0</v>
@@ -7154,13 +7154,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>214485.24</v>
+        <v>216766.73</v>
       </c>
       <c r="F64" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G64" s="16" t="n">
-        <v>0.101793</v>
+        <v>0.102876</v>
       </c>
       <c r="H64" s="9" t="n">
         <v>-0</v>
@@ -7169,7 +7169,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>220217.25</v>
+        <v>222498.74</v>
       </c>
     </row>
     <row r="65">
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="B65" s="9" t="n">
-        <v>213692.92</v>
+        <v>215956.47</v>
       </c>
       <c r="C65" s="9" t="n">
         <v>0</v>
@@ -7188,13 +7188,13 @@
         <v>0</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>213692.92</v>
+        <v>215956.47</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>0.101417</v>
+        <v>0.102491</v>
       </c>
       <c r="H65" s="9" t="n">
         <v>-0</v>
@@ -7203,7 +7203,7 @@
         <v>-5732.01</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>219424.93</v>
+        <v>221688.48</v>
       </c>
     </row>
     <row r="66">
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B66" s="9" t="n">
-        <v>214447.62</v>
+        <v>216721.28</v>
       </c>
       <c r="C66" s="9" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>214447.62</v>
+        <v>216721.28</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G66" s="16" t="n">
-        <v>0.101775</v>
+        <v>0.102854</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>-0</v>
@@ -7237,7 +7237,7 @@
         <v>-5653.01</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>220100.63</v>
+        <v>222374.29</v>
       </c>
     </row>
     <row r="67">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B67" s="9" t="n">
-        <v>213605</v>
+        <v>215819.8</v>
       </c>
       <c r="C67" s="9" t="n">
         <v>0</v>
@@ -7256,13 +7256,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>213605</v>
+        <v>215819.8</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>0.101375</v>
+        <v>0.102426</v>
       </c>
       <c r="H67" s="9" t="n">
         <v>-0</v>
@@ -7271,7 +7271,7 @@
         <v>-5521.95</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>219126.95</v>
+        <v>221341.75</v>
       </c>
     </row>
     <row r="68">
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>211847.57</v>
+        <v>213840.42</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>0</v>
@@ -7290,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>211847.57</v>
+        <v>213840.42</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0.100541</v>
+        <v>0.101487</v>
       </c>
       <c r="H68" s="9" t="n">
         <v>-0</v>
@@ -7305,7 +7305,7 @@
         <v>-5521.95</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>217369.52</v>
+        <v>219362.37</v>
       </c>
     </row>
     <row r="69">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="B69" s="9" t="n">
-        <v>217309.02</v>
+        <v>219340.27</v>
       </c>
       <c r="C69" s="9" t="n">
         <v>0</v>
@@ -7324,13 +7324,13 @@
         <v>0</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>217309.02</v>
+        <v>219340.27</v>
       </c>
       <c r="F69" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0.103133</v>
+        <v>0.104097</v>
       </c>
       <c r="H69" s="9" t="n">
         <v>-0</v>
@@ -7339,7 +7339,7 @@
         <v>-5520.2</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>222829.22</v>
+        <v>224860.47</v>
       </c>
     </row>
     <row r="70">
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>218038.95</v>
+        <v>220059.04</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>0</v>
@@ -7358,13 +7358,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>218038.95</v>
+        <v>220059.04</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0.10348</v>
+        <v>0.104438</v>
       </c>
       <c r="H70" s="9" t="n">
         <v>-0</v>
@@ -7373,7 +7373,7 @@
         <v>-5520.2</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>223559.15</v>
+        <v>225579.24</v>
       </c>
     </row>
     <row r="71">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="B71" s="9" t="n">
-        <v>221517.14</v>
+        <v>223547.17</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>221517.14</v>
+        <v>223547.17</v>
       </c>
       <c r="F71" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G71" s="16" t="n">
-        <v>0.10513</v>
+        <v>0.106094</v>
       </c>
       <c r="H71" s="9" t="n">
         <v>-0</v>
@@ -7407,7 +7407,7 @@
         <v>-5520.2</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>227037.34</v>
+        <v>229067.37</v>
       </c>
     </row>
     <row r="72">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>224053.84</v>
+        <v>226113.67</v>
       </c>
       <c r="C72" s="9" t="n">
         <v>0</v>
@@ -7426,13 +7426,13 @@
         <v>0</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>224053.84</v>
+        <v>226113.67</v>
       </c>
       <c r="F72" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>0.106334</v>
+        <v>0.107312</v>
       </c>
       <c r="H72" s="9" t="n">
         <v>-0</v>
@@ -7441,7 +7441,7 @@
         <v>-5520.2</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>229574.04</v>
+        <v>231633.87</v>
       </c>
     </row>
     <row r="73">
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="B73" s="9" t="n">
-        <v>223962.84</v>
+        <v>226026.38</v>
       </c>
       <c r="C73" s="9" t="n">
         <v>0</v>
@@ -7460,13 +7460,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>223962.84</v>
+        <v>226026.38</v>
       </c>
       <c r="F73" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>0.106291</v>
+        <v>0.10727</v>
       </c>
       <c r="H73" s="9" t="n">
         <v>-0</v>
@@ -7475,7 +7475,7 @@
         <v>-3745.7</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>227708.54</v>
+        <v>229772.08</v>
       </c>
     </row>
     <row r="74">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="B74" s="9" t="n">
-        <v>224638.47</v>
+        <v>226704.44</v>
       </c>
       <c r="C74" s="9" t="n">
         <v>0</v>
@@ -7494,13 +7494,13 @@
         <v>0</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>224638.47</v>
+        <v>226704.44</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G74" s="16" t="n">
-        <v>0.106612</v>
+        <v>0.107592</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>-0</v>
@@ -7509,7 +7509,7 @@
         <v>-3745.7</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>228384.17</v>
+        <v>230450.14</v>
       </c>
     </row>
     <row r="75">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="B75" s="9" t="n">
-        <v>224658.29</v>
+        <v>226728.3</v>
       </c>
       <c r="C75" s="9" t="n">
         <v>0</v>
@@ -7528,13 +7528,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>224658.29</v>
+        <v>226728.3</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G75" s="16" t="n">
-        <v>0.106621</v>
+        <v>0.107603</v>
       </c>
       <c r="H75" s="9" t="n">
         <v>-0</v>
@@ -7543,7 +7543,7 @@
         <v>-3745.7</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>228403.99</v>
+        <v>230474</v>
       </c>
     </row>
     <row r="76">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="B76" s="9" t="n">
-        <v>226590.28</v>
+        <v>228674.07</v>
       </c>
       <c r="C76" s="9" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>226590.28</v>
+        <v>228674.07</v>
       </c>
       <c r="F76" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G76" s="16" t="n">
-        <v>0.107538</v>
+        <v>0.108527</v>
       </c>
       <c r="H76" s="9" t="n">
         <v>-0</v>
@@ -7577,7 +7577,7 @@
         <v>-3745.7</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>230335.98</v>
+        <v>232419.77</v>
       </c>
     </row>
     <row r="77">
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B77" s="9" t="n">
-        <v>223419.85</v>
+        <v>225487.6</v>
       </c>
       <c r="C77" s="9" t="n">
         <v>0</v>
@@ -7596,13 +7596,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>223419.85</v>
+        <v>225487.6</v>
       </c>
       <c r="F77" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G77" s="16" t="n">
-        <v>0.106033</v>
+        <v>0.107015</v>
       </c>
       <c r="H77" s="9" t="n">
         <v>-0</v>
@@ -7611,7 +7611,7 @@
         <v>-3699.5</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>227119.35</v>
+        <v>229187.1</v>
       </c>
     </row>
     <row r="78">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>223430.79</v>
+        <v>225404.51</v>
       </c>
       <c r="C78" s="9" t="n">
         <v>0</v>
@@ -7630,13 +7630,13 @@
         <v>0</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>223430.79</v>
+        <v>225404.51</v>
       </c>
       <c r="F78" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0.106038</v>
+        <v>0.106975</v>
       </c>
       <c r="H78" s="9" t="n">
         <v>-0</v>
@@ -7645,7 +7645,7 @@
         <v>-3699.5</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>227130.29</v>
+        <v>229104.01</v>
       </c>
     </row>
     <row r="79">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B79" s="9" t="n">
-        <v>222807.66</v>
+        <v>224779.29</v>
       </c>
       <c r="C79" s="9" t="n">
         <v>0</v>
@@ -7664,13 +7664,13 @@
         <v>0</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>222807.66</v>
+        <v>224779.29</v>
       </c>
       <c r="F79" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0.105743</v>
+        <v>0.106678</v>
       </c>
       <c r="H79" s="9" t="n">
         <v>-0</v>
@@ -7679,7 +7679,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>226479.16</v>
+        <v>228450.79</v>
       </c>
     </row>
     <row r="80">
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="B80" s="9" t="n">
-        <v>222690.79</v>
+        <v>224656.56</v>
       </c>
       <c r="C80" s="9" t="n">
         <v>0</v>
@@ -7698,13 +7698,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>222690.79</v>
+        <v>224656.56</v>
       </c>
       <c r="F80" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G80" s="16" t="n">
-        <v>0.105687</v>
+        <v>0.10662</v>
       </c>
       <c r="H80" s="9" t="n">
         <v>-0</v>
@@ -7713,7 +7713,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>226362.29</v>
+        <v>228328.06</v>
       </c>
     </row>
     <row r="81">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B81" s="9" t="n">
-        <v>223631.68</v>
+        <v>225595.89</v>
       </c>
       <c r="C81" s="9" t="n">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>223631.68</v>
+        <v>225595.89</v>
       </c>
       <c r="F81" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G81" s="16" t="n">
-        <v>0.106134</v>
+        <v>0.107066</v>
       </c>
       <c r="H81" s="9" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>227303.18</v>
+        <v>229267.39</v>
       </c>
     </row>
     <row r="82">
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="B82" s="9" t="n">
-        <v>223709.38</v>
+        <v>225675.48</v>
       </c>
       <c r="C82" s="9" t="n">
         <v>0</v>
@@ -7766,13 +7766,13 @@
         <v>0</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>223709.38</v>
+        <v>225675.48</v>
       </c>
       <c r="F82" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G82" s="16" t="n">
-        <v>0.106171</v>
+        <v>0.107104</v>
       </c>
       <c r="H82" s="9" t="n">
         <v>-0</v>
@@ -7781,7 +7781,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>227380.88</v>
+        <v>229346.98</v>
       </c>
     </row>
     <row r="83">
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="B83" s="9" t="n">
-        <v>224858.58</v>
+        <v>226704.82</v>
       </c>
       <c r="C83" s="9" t="n">
         <v>0</v>
@@ -7800,13 +7800,13 @@
         <v>0</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>224858.58</v>
+        <v>226704.82</v>
       </c>
       <c r="F83" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G83" s="16" t="n">
-        <v>0.106716</v>
+        <v>0.107592</v>
       </c>
       <c r="H83" s="9" t="n">
         <v>-0</v>
@@ -7815,7 +7815,7 @@
         <v>-3671.5</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>228530.08</v>
+        <v>230376.32</v>
       </c>
     </row>
     <row r="84">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="B84" s="9" t="n">
-        <v>225360.69</v>
+        <v>227203.09</v>
       </c>
       <c r="C84" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         <v>0</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>225360.69</v>
+        <v>227203.09</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G84" s="16" t="n">
-        <v>0.106954</v>
+        <v>0.107829</v>
       </c>
       <c r="H84" s="9" t="n">
         <v>-0</v>
@@ -7849,7 +7849,7 @@
         <v>-3530.99</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>228891.68</v>
+        <v>230734.08</v>
       </c>
     </row>
     <row r="85">
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="B85" s="9" t="n">
-        <v>223782.71</v>
+        <v>225616.95</v>
       </c>
       <c r="C85" s="9" t="n">
         <v>0</v>
@@ -7868,13 +7868,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>223782.71</v>
+        <v>225616.95</v>
       </c>
       <c r="F85" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G85" s="16" t="n">
-        <v>0.106206</v>
+        <v>0.107076</v>
       </c>
       <c r="H85" s="9" t="n">
         <v>-0</v>
@@ -7883,7 +7883,7 @@
         <v>-3530.99</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>227313.7</v>
+        <v>229147.94</v>
       </c>
     </row>
     <row r="86">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="B86" s="9" t="n">
-        <v>224533.75</v>
+        <v>226361.74</v>
       </c>
       <c r="C86" s="9" t="n">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>224533.75</v>
+        <v>226361.74</v>
       </c>
       <c r="F86" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0.106562</v>
+        <v>0.107429</v>
       </c>
       <c r="H86" s="9" t="n">
         <v>-0</v>
@@ -7917,7 +7917,7 @@
         <v>-1630.99</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>226164.74</v>
+        <v>227992.73</v>
       </c>
     </row>
     <row r="87">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="B87" s="9" t="n">
-        <v>225085.17</v>
+        <v>226924.78</v>
       </c>
       <c r="C87" s="9" t="n">
         <v>0</v>
@@ -7936,13 +7936,13 @@
         <v>0</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>225085.17</v>
+        <v>226924.78</v>
       </c>
       <c r="F87" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G87" s="16" t="n">
-        <v>0.106824</v>
+        <v>0.107697</v>
       </c>
       <c r="H87" s="9" t="n">
         <v>-0</v>
@@ -7951,7 +7951,7 @@
         <v>-1630.99</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>226716.16</v>
+        <v>228555.77</v>
       </c>
     </row>
     <row r="88">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="B88" s="9" t="n">
-        <v>223495.65</v>
+        <v>225308.04</v>
       </c>
       <c r="C88" s="9" t="n">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         <v>0</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>223495.65</v>
+        <v>225308.04</v>
       </c>
       <c r="F88" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G88" s="16" t="n">
-        <v>0.106069</v>
+        <v>0.106929</v>
       </c>
       <c r="H88" s="9" t="n">
         <v>-0</v>
@@ -7985,7 +7985,7 @@
         <v>-1555.56</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>225051.21</v>
+        <v>226863.6</v>
       </c>
     </row>
     <row r="89">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="B89" s="9" t="n">
-        <v>223193.17</v>
+        <v>225060.22</v>
       </c>
       <c r="C89" s="9" t="n">
         <v>0</v>
@@ -8004,13 +8004,13 @@
         <v>0</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>223193.17</v>
+        <v>225060.22</v>
       </c>
       <c r="F89" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G89" s="16" t="n">
-        <v>0.105926</v>
+        <v>0.106812</v>
       </c>
       <c r="H89" s="9" t="n">
         <v>-0</v>
@@ -8019,7 +8019,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>228096.73</v>
+        <v>229963.78</v>
       </c>
     </row>
     <row r="90">
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="B90" s="9" t="n">
-        <v>222914.17</v>
+        <v>224761.02</v>
       </c>
       <c r="C90" s="9" t="n">
         <v>0</v>
@@ -8038,13 +8038,13 @@
         <v>0</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>222914.17</v>
+        <v>224761.02</v>
       </c>
       <c r="F90" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G90" s="16" t="n">
-        <v>0.105793</v>
+        <v>0.10667</v>
       </c>
       <c r="H90" s="9" t="n">
         <v>-0</v>
@@ -8053,7 +8053,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>227817.73</v>
+        <v>229664.58</v>
       </c>
     </row>
     <row r="91">
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="B91" s="9" t="n">
-        <v>220398.21</v>
+        <v>222198.46</v>
       </c>
       <c r="C91" s="9" t="n">
         <v>0</v>
@@ -8072,13 +8072,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>220398.21</v>
+        <v>222198.46</v>
       </c>
       <c r="F91" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G91" s="16" t="n">
-        <v>0.104599</v>
+        <v>0.105454</v>
       </c>
       <c r="H91" s="9" t="n">
         <v>-0</v>
@@ -8087,7 +8087,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>225301.77</v>
+        <v>227102.02</v>
       </c>
     </row>
     <row r="92">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B92" s="9" t="n">
-        <v>220604.83</v>
+        <v>222399.76</v>
       </c>
       <c r="C92" s="9" t="n">
         <v>0</v>
@@ -8106,13 +8106,13 @@
         <v>0</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>220604.83</v>
+        <v>222399.76</v>
       </c>
       <c r="F92" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G92" s="16" t="n">
-        <v>0.104697</v>
+        <v>0.105549</v>
       </c>
       <c r="H92" s="9" t="n">
         <v>-0</v>
@@ -8121,7 +8121,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>225508.39</v>
+        <v>227303.32</v>
       </c>
     </row>
     <row r="93">
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="B93" s="9" t="n">
-        <v>220696.27</v>
+        <v>222356.65</v>
       </c>
       <c r="C93" s="9" t="n">
         <v>0</v>
@@ -8140,13 +8140,13 @@
         <v>0</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>220696.27</v>
+        <v>222356.65</v>
       </c>
       <c r="F93" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G93" s="16" t="n">
-        <v>0.104741</v>
+        <v>0.105529</v>
       </c>
       <c r="H93" s="9" t="n">
         <v>-0</v>
@@ -8155,7 +8155,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>225599.83</v>
+        <v>227260.21</v>
       </c>
     </row>
     <row r="94">
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="B94" s="9" t="n">
-        <v>222741.28</v>
+        <v>224437.62</v>
       </c>
       <c r="C94" s="9" t="n">
         <v>0</v>
@@ -8174,13 +8174,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>222741.28</v>
+        <v>224437.62</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G94" s="16" t="n">
-        <v>0.105711</v>
+        <v>0.106516</v>
       </c>
       <c r="H94" s="9" t="n">
         <v>-0</v>
@@ -8189,7 +8189,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>227644.84</v>
+        <v>229341.18</v>
       </c>
     </row>
     <row r="95">
@@ -8199,7 +8199,7 @@
         </is>
       </c>
       <c r="B95" s="9" t="n">
-        <v>221246.5</v>
+        <v>222924.68</v>
       </c>
       <c r="C95" s="9" t="n">
         <v>0</v>
@@ -8208,13 +8208,13 @@
         <v>0</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>221246.5</v>
+        <v>222924.68</v>
       </c>
       <c r="F95" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G95" s="16" t="n">
-        <v>0.105002</v>
+        <v>0.105798</v>
       </c>
       <c r="H95" s="9" t="n">
         <v>-0</v>
@@ -8223,7 +8223,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>226150.06</v>
+        <v>227828.24</v>
       </c>
     </row>
     <row r="96">
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="B96" s="9" t="n">
-        <v>221893.42</v>
+        <v>223585.49</v>
       </c>
       <c r="C96" s="9" t="n">
         <v>0</v>
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>221893.42</v>
+        <v>223585.49</v>
       </c>
       <c r="F96" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G96" s="16" t="n">
-        <v>0.105309</v>
+        <v>0.106112</v>
       </c>
       <c r="H96" s="9" t="n">
         <v>-0</v>
@@ -8257,7 +8257,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>226796.98</v>
+        <v>228489.05</v>
       </c>
     </row>
     <row r="97">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="B97" s="9" t="n">
-        <v>220861.61</v>
+        <v>222512.7</v>
       </c>
       <c r="C97" s="9" t="n">
         <v>0</v>
@@ -8276,13 +8276,13 @@
         <v>0</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>220861.61</v>
+        <v>222512.7</v>
       </c>
       <c r="F97" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G97" s="16" t="n">
-        <v>0.104819</v>
+        <v>0.105603</v>
       </c>
       <c r="H97" s="9" t="n">
         <v>-0</v>
@@ -8291,7 +8291,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>225765.17</v>
+        <v>227416.26</v>
       </c>
     </row>
     <row r="98">
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="B98" s="9" t="n">
-        <v>221019.49</v>
+        <v>222677.02</v>
       </c>
       <c r="C98" s="9" t="n">
         <v>0</v>
@@ -8310,13 +8310,13 @@
         <v>0</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>221019.49</v>
+        <v>222677.02</v>
       </c>
       <c r="F98" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G98" s="16" t="n">
-        <v>0.104894</v>
+        <v>0.105681</v>
       </c>
       <c r="H98" s="9" t="n">
         <v>-0</v>
@@ -8325,7 +8325,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>225923.05</v>
+        <v>227580.58</v>
       </c>
     </row>
     <row r="99">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="B99" s="9" t="n">
-        <v>218999.2</v>
+        <v>220638.8</v>
       </c>
       <c r="C99" s="9" t="n">
         <v>0</v>
@@ -8344,13 +8344,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>218999.2</v>
+        <v>220638.8</v>
       </c>
       <c r="F99" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G99" s="16" t="n">
-        <v>0.103935</v>
+        <v>0.104713</v>
       </c>
       <c r="H99" s="9" t="n">
         <v>-0</v>
@@ -8359,7 +8359,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>223902.76</v>
+        <v>225542.36</v>
       </c>
     </row>
     <row r="100">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B100" s="9" t="n">
-        <v>218651.59</v>
+        <v>220300.28</v>
       </c>
       <c r="C100" s="9" t="n">
         <v>0</v>
@@ -8378,13 +8378,13 @@
         <v>0</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>218651.59</v>
+        <v>220300.28</v>
       </c>
       <c r="F100" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G100" s="16" t="n">
-        <v>0.10377</v>
+        <v>0.104553</v>
       </c>
       <c r="H100" s="9" t="n">
         <v>-0</v>
@@ -8393,7 +8393,7 @@
         <v>-4903.56</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>223555.15</v>
+        <v>225203.84</v>
       </c>
     </row>
     <row r="101">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="B101" s="9" t="n">
-        <v>220806.2</v>
+        <v>222457.28</v>
       </c>
       <c r="C101" s="9" t="n">
         <v>0</v>
@@ -8412,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>220806.2</v>
+        <v>222457.28</v>
       </c>
       <c r="F101" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G101" s="16" t="n">
-        <v>0.104793</v>
+        <v>0.105576</v>
       </c>
       <c r="H101" s="9" t="n">
         <v>-0</v>
@@ -8427,7 +8427,7 @@
         <v>-2876.06</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>223682.26</v>
+        <v>225333.34</v>
       </c>
     </row>
     <row r="102">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B102" s="9" t="n">
-        <v>224058.87</v>
+        <v>225684.43</v>
       </c>
       <c r="C102" s="9" t="n">
         <v>0</v>
@@ -8446,13 +8446,13 @@
         <v>0</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>224058.87</v>
+        <v>225684.43</v>
       </c>
       <c r="F102" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G102" s="16" t="n">
-        <v>0.106337</v>
+        <v>0.107108</v>
       </c>
       <c r="H102" s="9" t="n">
         <v>-0</v>
@@ -8461,7 +8461,7 @@
         <v>-7172.56</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>231231.43</v>
+        <v>232856.99</v>
       </c>
     </row>
     <row r="103">
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="B103" s="9" t="n">
-        <v>227065.25</v>
+        <v>228582.68</v>
       </c>
       <c r="C103" s="9" t="n">
         <v>0</v>
@@ -8480,13 +8480,13 @@
         <v>0</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>227065.25</v>
+        <v>228582.68</v>
       </c>
       <c r="F103" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G103" s="16" t="n">
-        <v>0.107763</v>
+        <v>0.108484</v>
       </c>
       <c r="H103" s="9" t="n">
         <v>-0</v>
@@ -8495,7 +8495,7 @@
         <v>-4847.62</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>231912.87</v>
+        <v>233430.3</v>
       </c>
     </row>
     <row r="104">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="B104" s="9" t="n">
-        <v>223676.22</v>
+        <v>225164.52</v>
       </c>
       <c r="C104" s="9" t="n">
         <v>0</v>
@@ -8514,13 +8514,13 @@
         <v>0</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>223676.22</v>
+        <v>225164.52</v>
       </c>
       <c r="F104" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G104" s="16" t="n">
-        <v>0.106155</v>
+        <v>0.106861</v>
       </c>
       <c r="H104" s="9" t="n">
         <v>-0</v>
@@ -8529,7 +8529,7 @@
         <v>-4828.86</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>228505.08</v>
+        <v>229993.38</v>
       </c>
     </row>
     <row r="105">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B105" s="9" t="n">
-        <v>219588.58</v>
+        <v>220966.06</v>
       </c>
       <c r="C105" s="9" t="n">
         <v>0</v>
@@ -8548,13 +8548,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>219588.58</v>
+        <v>220966.06</v>
       </c>
       <c r="F105" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G105" s="16" t="n">
-        <v>0.104215</v>
+        <v>0.104869</v>
       </c>
       <c r="H105" s="9" t="n">
         <v>-0</v>
@@ -8563,7 +8563,7 @@
         <v>-4828.86</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>224417.44</v>
+        <v>225794.92</v>
       </c>
     </row>
     <row r="106">
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="B106" s="9" t="n">
-        <v>221482.47</v>
+        <v>222812.49</v>
       </c>
       <c r="C106" s="9" t="n">
         <v>0</v>
@@ -8582,13 +8582,13 @@
         <v>0</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>221482.47</v>
+        <v>222812.49</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G106" s="16" t="n">
-        <v>0.105114</v>
+        <v>0.105745</v>
       </c>
       <c r="H106" s="9" t="n">
         <v>-0</v>
@@ -8597,7 +8597,7 @@
         <v>-4828.86</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>226311.33</v>
+        <v>227641.35</v>
       </c>
     </row>
     <row r="107">
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="B107" s="9" t="n">
-        <v>219077.25</v>
+        <v>220422.95</v>
       </c>
       <c r="C107" s="9" t="n">
         <v>0</v>
@@ -8616,13 +8616,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>219077.25</v>
+        <v>220422.95</v>
       </c>
       <c r="F107" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G107" s="16" t="n">
-        <v>0.103972</v>
+        <v>0.104611</v>
       </c>
       <c r="H107" s="9" t="n">
         <v>-0</v>
@@ -8631,7 +8631,7 @@
         <v>-4828.86</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>223906.11</v>
+        <v>225251.81</v>
       </c>
     </row>
     <row r="108">
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B108" s="9" t="n">
-        <v>217418.52</v>
+        <v>218749.24</v>
       </c>
       <c r="C108" s="9" t="n">
         <v>0</v>
@@ -8650,13 +8650,13 @@
         <v>0</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>217418.52</v>
+        <v>218749.24</v>
       </c>
       <c r="F108" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G108" s="16" t="n">
-        <v>0.103185</v>
+        <v>0.103817</v>
       </c>
       <c r="H108" s="9" t="n">
         <v>-0</v>
@@ -8665,7 +8665,7 @@
         <v>-4753.43</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>222171.95</v>
+        <v>223502.67</v>
       </c>
     </row>
     <row r="109">
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="B109" s="9" t="n">
-        <v>217566.84</v>
+        <v>218918.57</v>
       </c>
       <c r="C109" s="9" t="n">
         <v>0</v>
@@ -8684,13 +8684,13 @@
         <v>0</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>217566.84</v>
+        <v>218918.57</v>
       </c>
       <c r="F109" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G109" s="16" t="n">
-        <v>0.103256</v>
+        <v>0.103897</v>
       </c>
       <c r="H109" s="9" t="n">
         <v>-0</v>
@@ -8699,7 +8699,7 @@
         <v>-4753.43</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>222320.27</v>
+        <v>223672</v>
       </c>
     </row>
     <row r="110">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>216034.74</v>
+        <v>217389.65</v>
       </c>
       <c r="C110" s="9" t="n">
         <v>0</v>
@@ -8718,13 +8718,13 @@
         <v>0</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>216034.74</v>
+        <v>217389.65</v>
       </c>
       <c r="F110" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G110" s="16" t="n">
-        <v>0.102528</v>
+        <v>0.103171</v>
       </c>
       <c r="H110" s="9" t="n">
         <v>-0</v>
@@ -8733,7 +8733,7 @@
         <v>-4753.43</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>220788.17</v>
+        <v>222143.08</v>
       </c>
     </row>
     <row r="111">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="B111" s="9" t="n">
-        <v>214529.24</v>
+        <v>215856.81</v>
       </c>
       <c r="C111" s="9" t="n">
         <v>0</v>
@@ -8752,13 +8752,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>214529.24</v>
+        <v>215856.81</v>
       </c>
       <c r="F111" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G111" s="16" t="n">
-        <v>0.101814</v>
+        <v>0.102444</v>
       </c>
       <c r="H111" s="9" t="n">
         <v>-0</v>
@@ -8767,7 +8767,7 @@
         <v>-4753.43</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>219282.67</v>
+        <v>220610.24</v>
       </c>
     </row>
     <row r="112">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="B112" s="9" t="n">
-        <v>213990.5</v>
+        <v>215336.16</v>
       </c>
       <c r="C112" s="9" t="n">
         <v>0</v>
@@ -8786,13 +8786,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>213990.5</v>
+        <v>215336.16</v>
       </c>
       <c r="F112" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G112" s="16" t="n">
-        <v>0.101558</v>
+        <v>0.102197</v>
       </c>
       <c r="H112" s="9" t="n">
         <v>-0</v>
@@ -8801,7 +8801,7 @@
         <v>-4753.43</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>218743.93</v>
+        <v>220089.59</v>
       </c>
     </row>
     <row r="113">
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>215845.54</v>
+        <v>217152.76</v>
       </c>
       <c r="C113" s="9" t="n">
         <v>0</v>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>215845.54</v>
+        <v>217152.76</v>
       </c>
       <c r="F113" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G113" s="16" t="n">
-        <v>0.102439</v>
+        <v>0.103059</v>
       </c>
       <c r="H113" s="9" t="n">
         <v>-0</v>
@@ -8835,7 +8835,7 @@
         <v>-8796.700000000001</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>224642.24</v>
+        <v>225949.46</v>
       </c>
     </row>
     <row r="114">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="B114" s="9" t="n">
-        <v>216565.01</v>
+        <v>217891.22</v>
       </c>
       <c r="C114" s="9" t="n">
         <v>0</v>
@@ -8854,13 +8854,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>216565.01</v>
+        <v>217891.22</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G114" s="16" t="n">
-        <v>0.10278</v>
+        <v>0.103409</v>
       </c>
       <c r="H114" s="9" t="n">
         <v>-0</v>
@@ -8869,7 +8869,7 @@
         <v>-8769.309999999999</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>225334.32</v>
+        <v>226660.53</v>
       </c>
     </row>
     <row r="115">
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="B115" s="9" t="n">
-        <v>211533.28</v>
+        <v>212817.84</v>
       </c>
       <c r="C115" s="9" t="n">
         <v>0</v>
@@ -8888,13 +8888,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>211533.28</v>
+        <v>212817.84</v>
       </c>
       <c r="F115" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G115" s="16" t="n">
-        <v>0.100392</v>
+        <v>0.101002</v>
       </c>
       <c r="H115" s="9" t="n">
         <v>-0</v>
@@ -8903,7 +8903,7 @@
         <v>-8769.309999999999</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>220302.59</v>
+        <v>221587.15</v>
       </c>
     </row>
     <row r="116">
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B116" s="9" t="n">
-        <v>211628.14</v>
+        <v>212898.28</v>
       </c>
       <c r="C116" s="9" t="n">
         <v>0</v>
@@ -8922,13 +8922,13 @@
         <v>0</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>211628.14</v>
+        <v>212898.28</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G116" s="16" t="n">
-        <v>0.100437</v>
+        <v>0.10104</v>
       </c>
       <c r="H116" s="9" t="n">
         <v>-0</v>
@@ -8937,7 +8937,7 @@
         <v>-13749.65</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>225377.79</v>
+        <v>226647.93</v>
       </c>
     </row>
     <row r="117">
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B117" s="9" t="n">
-        <v>210846.56</v>
+        <v>212107.49</v>
       </c>
       <c r="C117" s="9" t="n">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>210846.56</v>
+        <v>212107.49</v>
       </c>
       <c r="F117" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G117" s="16" t="n">
-        <v>0.100066</v>
+        <v>0.100665</v>
       </c>
       <c r="H117" s="9" t="n">
         <v>-0</v>
@@ -8971,7 +8971,7 @@
         <v>-13749.65</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>224596.21</v>
+        <v>225857.14</v>
       </c>
     </row>
     <row r="118">
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B118" s="9" t="n">
-        <v>211298.74</v>
+        <v>212553.61</v>
       </c>
       <c r="C118" s="9" t="n">
         <v>0</v>
@@ -8990,13 +8990,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>211298.74</v>
+        <v>212553.61</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G118" s="16" t="n">
-        <v>0.100281</v>
+        <v>0.100876</v>
       </c>
       <c r="H118" s="9" t="n">
         <v>-0</v>
@@ -9005,7 +9005,7 @@
         <v>-13749.65</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>225048.39</v>
+        <v>226303.26</v>
       </c>
     </row>
     <row r="119">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B119" s="9" t="n">
-        <v>211588.09</v>
+        <v>212850.12</v>
       </c>
       <c r="C119" s="9" t="n">
         <v>0</v>
@@ -9024,13 +9024,13 @@
         <v>0</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>211588.09</v>
+        <v>212850.12</v>
       </c>
       <c r="F119" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G119" s="16" t="n">
-        <v>0.100418</v>
+        <v>0.101017</v>
       </c>
       <c r="H119" s="9" t="n">
         <v>-0</v>
@@ -9039,7 +9039,7 @@
         <v>-13749.65</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>225337.74</v>
+        <v>226599.77</v>
       </c>
     </row>
     <row r="120">
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="B120" s="9" t="n">
-        <v>210790.17</v>
+        <v>212041.53</v>
       </c>
       <c r="C120" s="9" t="n">
         <v>0</v>
@@ -9058,13 +9058,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>210790.17</v>
+        <v>212041.53</v>
       </c>
       <c r="F120" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G120" s="16" t="n">
-        <v>0.100039</v>
+        <v>0.100633</v>
       </c>
       <c r="H120" s="9" t="n">
         <v>-0</v>
@@ -9073,7 +9073,7 @@
         <v>-13749.65</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>224539.82</v>
+        <v>225791.18</v>
       </c>
     </row>
     <row r="121">
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="B121" s="9" t="n">
-        <v>215346.73</v>
+        <v>216640.15</v>
       </c>
       <c r="C121" s="9" t="n">
         <v>0</v>
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>215346.73</v>
+        <v>216640.15</v>
       </c>
       <c r="F121" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G121" s="16" t="n">
-        <v>0.102202</v>
+        <v>0.102816</v>
       </c>
       <c r="H121" s="9" t="n">
         <v>-0</v>
@@ -9107,7 +9107,7 @@
         <v>-16571.02</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>231917.75</v>
+        <v>233211.17</v>
       </c>
     </row>
     <row r="122">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="B122" s="9" t="n">
-        <v>215850.71</v>
+        <v>217150.4</v>
       </c>
       <c r="C122" s="9" t="n">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>215850.71</v>
+        <v>217150.4</v>
       </c>
       <c r="F122" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G122" s="16" t="n">
-        <v>0.102441</v>
+        <v>0.103058</v>
       </c>
       <c r="H122" s="9" t="n">
         <v>-0</v>
@@ -9141,7 +9141,7 @@
         <v>-16538.54</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>232389.25</v>
+        <v>233688.94</v>
       </c>
     </row>
     <row r="123">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="B123" s="9" t="n">
-        <v>214046.73</v>
+        <v>215332.14</v>
       </c>
       <c r="C123" s="9" t="n">
         <v>0</v>
@@ -9160,13 +9160,13 @@
         <v>0</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>214046.73</v>
+        <v>215332.14</v>
       </c>
       <c r="F123" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G123" s="16" t="n">
-        <v>0.101585</v>
+        <v>0.102195</v>
       </c>
       <c r="H123" s="9" t="n">
         <v>-0</v>
@@ -9175,7 +9175,7 @@
         <v>-16538.54</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>230585.27</v>
+        <v>231870.68</v>
       </c>
     </row>
     <row r="124">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="B124" s="9" t="n">
-        <v>219103.72</v>
+        <v>219401.84</v>
       </c>
       <c r="C124" s="9" t="n">
         <v>0</v>
@@ -9194,13 +9194,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>219103.72</v>
+        <v>219401.84</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G124" s="16" t="n">
-        <v>0.103985</v>
+        <v>0.104126</v>
       </c>
       <c r="H124" s="9" t="n">
         <v>-0</v>
@@ -9209,7 +9209,7 @@
         <v>-16538.54</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>235642.26</v>
+        <v>235940.38</v>
       </c>
     </row>
     <row r="125">
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="B125" s="9" t="n">
-        <v>223437.37</v>
+        <v>223731.22</v>
       </c>
       <c r="C125" s="9" t="n">
         <v>0</v>
@@ -9228,13 +9228,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>223437.37</v>
+        <v>223731.22</v>
       </c>
       <c r="F125" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G125" s="16" t="n">
-        <v>0.106042</v>
+        <v>0.106181</v>
       </c>
       <c r="H125" s="9" t="n">
         <v>-0</v>
@@ -9243,7 +9243,7 @@
         <v>-16538.54</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>239975.91</v>
+        <v>240269.76</v>
       </c>
     </row>
     <row r="126">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B126" s="9" t="n">
-        <v>221948.32</v>
+        <v>222232.03</v>
       </c>
       <c r="C126" s="9" t="n">
         <v>0</v>
@@ -9262,13 +9262,13 @@
         <v>0</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>221948.32</v>
+        <v>222232.03</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G126" s="16" t="n">
-        <v>0.105335</v>
+        <v>0.10547</v>
       </c>
       <c r="H126" s="9" t="n">
         <v>-0</v>
@@ -9277,7 +9277,7 @@
         <v>-16477.31</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>238425.63</v>
+        <v>238709.34</v>
       </c>
     </row>
     <row r="127">
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="B127" s="9" t="n">
-        <v>223514.87</v>
+        <v>223810.37</v>
       </c>
       <c r="C127" s="9" t="n">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>223514.87</v>
+        <v>223810.37</v>
       </c>
       <c r="F127" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G127" s="16" t="n">
-        <v>0.106078</v>
+        <v>0.106219</v>
       </c>
       <c r="H127" s="9" t="n">
         <v>-0</v>
@@ -9311,7 +9311,7 @@
         <v>-17458.51</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>240973.38</v>
+        <v>241268.88</v>
       </c>
     </row>
     <row r="128">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="B128" s="9" t="n">
-        <v>221829.33</v>
+        <v>222119.01</v>
       </c>
       <c r="C128" s="9" t="n">
         <v>0</v>
@@ -9330,13 +9330,13 @@
         <v>0</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>221829.33</v>
+        <v>222119.01</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G128" s="16" t="n">
-        <v>0.105278</v>
+        <v>0.105416</v>
       </c>
       <c r="H128" s="9" t="n">
         <v>-0</v>
@@ -9345,7 +9345,7 @@
         <v>-17050.02</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>238879.35</v>
+        <v>239169.03</v>
       </c>
     </row>
     <row r="129">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="B129" s="9" t="n">
-        <v>222341.17</v>
+        <v>222627.97</v>
       </c>
       <c r="C129" s="9" t="n">
         <v>0</v>
@@ -9364,13 +9364,13 @@
         <v>0</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>222341.17</v>
+        <v>222627.97</v>
       </c>
       <c r="F129" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G129" s="16" t="n">
-        <v>0.105521</v>
+        <v>0.105657</v>
       </c>
       <c r="H129" s="9" t="n">
         <v>-0</v>
@@ -9379,7 +9379,7 @@
         <v>-17050.02</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>239391.19</v>
+        <v>239677.99</v>
       </c>
     </row>
     <row r="130">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="B135" s="9" t="n">
-        <v>230555.13</v>
+        <v>230169.5</v>
       </c>
       <c r="C135" s="9" t="n">
         <v>0</v>
@@ -9568,13 +9568,13 @@
         <v>0</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>230555.13</v>
+        <v>230169.5</v>
       </c>
       <c r="F135" s="8" t="n">
         <v>2107072.57</v>
       </c>
       <c r="G135" s="16" t="n">
-        <v>0.10942</v>
+        <v>0.109237</v>
       </c>
       <c r="H135" s="9" t="n">
         <v>-0</v>
@@ -9583,7 +9583,347 @@
         <v>-12809.08</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>243364.21</v>
+        <v>242978.58</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>229943.72</v>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>229943.72</v>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G136" s="16" t="n">
+        <v>0.109129</v>
+      </c>
+      <c r="H136" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I136" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>242752.8</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>228509.37</v>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>228509.37</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G137" s="16" t="n">
+        <v>0.108449</v>
+      </c>
+      <c r="H137" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I137" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>241318.45</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>227029.94</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="9" t="n">
+        <v>227029.94</v>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G138" s="16" t="n">
+        <v>0.107747</v>
+      </c>
+      <c r="H138" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I138" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>239839.02</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>224740.8</v>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>224740.8</v>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G139" s="16" t="n">
+        <v>0.10666</v>
+      </c>
+      <c r="H139" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I139" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>237549.88</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="n">
+        <v>226270.94</v>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="9" t="n">
+        <v>226270.94</v>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G140" s="16" t="n">
+        <v>0.107386</v>
+      </c>
+      <c r="H140" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I140" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>239080.02</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="n">
+        <v>228696.91</v>
+      </c>
+      <c r="C141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>228696.91</v>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G141" s="16" t="n">
+        <v>0.108538</v>
+      </c>
+      <c r="H141" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I141" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>241505.99</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="n">
+        <v>232030.11</v>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="9" t="n">
+        <v>232030.11</v>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G142" s="16" t="n">
+        <v>0.11012</v>
+      </c>
+      <c r="H142" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I142" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>244839.19</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="n">
+        <v>233212.42</v>
+      </c>
+      <c r="C143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>233212.42</v>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G143" s="16" t="n">
+        <v>0.110681</v>
+      </c>
+      <c r="H143" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I143" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>246021.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="n">
+        <v>233332.72</v>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="9" t="n">
+        <v>233332.72</v>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G144" s="16" t="n">
+        <v>0.110738</v>
+      </c>
+      <c r="H144" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I144" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>246141.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>233332.72</v>
+      </c>
+      <c r="C145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>233332.72</v>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>2107072.57</v>
+      </c>
+      <c r="G145" s="16" t="n">
+        <v>0.110738</v>
+      </c>
+      <c r="H145" s="9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I145" s="9" t="n">
+        <v>-12809.08</v>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>246141.8</v>
       </c>
     </row>
   </sheetData>
